--- a/output/stage1_task_input_table.xlsx
+++ b/output/stage1_task_input_table.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ED54"/>
+  <dimension ref="A1:ED57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,20 +1125,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Y5-9</t>
+          <t>V5-4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>00079230</t>
+          <t>00079421</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>30040-AG00-1030X200F-ABK0C</t>
+          <t>30040-AY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>30020-KG00-1030X200F-ABK0C</t>
+          <t>30020-BY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="Q2" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>スライス,巻返し</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00073419</t>
+          <t>00073579</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1210,26 +1210,26 @@
         <v>1</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD2" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AE2" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AF2" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" s="1" t="n">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="AK2" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
@@ -1571,20 +1571,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>015</t>
         </is>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46149</v>
+        <v>46136</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>V5-4</t>
+          <t>Y5-7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>00079421</t>
+          <t>00079148</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1599,24 +1599,24 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>30040-AY00-1000X200F-A   C</t>
+          <t>30044-AG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>30020-BY00-1000X200F-A   C</t>
+          <t>30022-BG00-1000X200F-AWH1C</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="Q3" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>スライス,巻返し</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00073579</t>
+          <t>00073355</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>46154</v>
       </c>
       <c r="AI3" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1690,19 +1690,19 @@
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="AM3" t="n">
-        <v>4000</v>
+        <v>2200</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="AO3" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1801,10 +1801,10 @@
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
@@ -2017,20 +2017,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Y5-7</t>
+          <t>Y5-11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>00079148</t>
+          <t>00079286</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2045,20 +2045,20 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>30044-AG00-1000X200F-AWH1C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>30022-BG00-1000X200F-AWH1C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="Q4" t="n">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>00073355</t>
+          <t>00073464</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2102,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -2115,20 +2115,20 @@
         </is>
       </c>
       <c r="AD4" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="AE4" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="AF4" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="AI4" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2247,16 +2247,16 @@
         <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>013</t>
         </is>
       </c>
       <c r="H5" s="1" t="n">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Y5-11</t>
+          <t>Y5-12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>00079286</t>
+          <t>00079287</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>00073464</t>
+          <t>00073465</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>7800</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>1200</v>
+        <v>6600</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46140</v>
+        <v>46149</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Y5-12</t>
+          <t>Y5-18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>00079287</t>
+          <t>00079396</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2937,24 +2937,24 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30040-AY00- 960X250F-A   C</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30020-BY00- 450X250F-A   C</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="Q6" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>スリット,スライス</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>00073465</t>
+          <t>00073550</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -2994,33 +2994,33 @@
         <v>1</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AD6" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="AE6" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -3157,10 +3157,10 @@
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>2400</v>
+        <v>5000</v>
       </c>
       <c r="CC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
@@ -3355,20 +3355,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46149</v>
+        <v>46140</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Y5-18</t>
+          <t>Y5-13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>00079396</t>
+          <t>00079288</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3383,24 +3383,24 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30040-AY00- 960X250F-A   C</t>
+          <t>30040-AG00- 780X300F-A   C</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>30020-BY00- 450X250F-A   C</t>
+          <t>30020-BG00- 780X300F-A   V</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3000</v>
+        <v>5100</v>
       </c>
       <c r="Q7" t="n">
-        <v>12000</v>
+        <v>10200</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>スリット,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>00073550</t>
+          <t>00073466</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3440,11 +3440,11 @@
         <v>1</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3453,17 +3453,17 @@
         </is>
       </c>
       <c r="AD7" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="AE7" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="AI7" s="1" t="n">
         <v>46161</v>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>6000</v>
+        <v>5100</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>6000</v>
+        <v>5100</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3603,10 +3603,10 @@
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>1000</v>
+        <v>5100</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
@@ -3801,20 +3801,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46140</v>
+        <v>46149</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Y5-13</t>
+          <t>Y5-15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>00079288</t>
+          <t>00079392</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3829,20 +3829,20 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>30040-AG00- 780X300F-A   C</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>30020-BG00- 780X300F-A   V</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>5100</v>
+        <v>8000</v>
       </c>
       <c r="Q8" t="n">
-        <v>10200</v>
+        <v>16000</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>00073466</t>
+          <t>00073551</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3895,24 +3895,24 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD8" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="AE8" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>5100</v>
+        <v>8000</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>5100</v>
+        <v>8000</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -4052,13 +4052,13 @@
         <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>5100</v>
+        <v>1200</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
@@ -4247,20 +4247,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Y5-30</t>
+          <t>Y5-16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>00079479</t>
+          <t>00079393</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4275,24 +4275,24 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>30066-AY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-ABK0C</t>
+          <t>30033-BY00- 640X200F-AGA0C</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>200</v>
+        <v>8000</v>
       </c>
       <c r="Q9" t="n">
-        <v>400</v>
+        <v>16000</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>00073651</t>
+          <t>00073552</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4332,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -4345,20 +4345,20 @@
         </is>
       </c>
       <c r="AD9" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="AE9" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" s="1" t="n">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>200</v>
+        <v>8000</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>200</v>
+        <v>8000</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -4504,10 +4504,10 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="CG9" t="n">
         <v>0</v>
@@ -4683,30 +4683,30 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Y5-30</t>
+          <t>Y5-17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>00079479</t>
+          <t>00079395</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4721,24 +4721,24 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>30040-AY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-ABK0C</t>
+          <t>30020-BY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="Q10" t="n">
-        <v>400</v>
+        <v>10000</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>00073650</t>
+          <t>00073553</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4778,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -4787,24 +4787,24 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AD10" s="1" t="n">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="AE10" s="1" t="n">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" s="1" t="n">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>400</v>
+        <v>5000</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -4824,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>400</v>
+        <v>5000</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5119,22 +5119,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5147,44 +5147,44 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Y5-15</t>
+          <t>W5-5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>00079392</t>
+          <t>00079411</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="Q11" t="n">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>00073551</t>
+          <t>00073567</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5224,33 +5224,31 @@
         <v>1</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AD11" s="1" t="n">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="AE11" s="1" t="n">
-        <v>46168</v>
-      </c>
-      <c r="AF11" s="1" t="n">
-        <v>46168</v>
-      </c>
+        <v>46164</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" s="1" t="n">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -5258,7 +5256,7 @@
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -5270,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -5378,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -5387,16 +5385,16 @@
         <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="CC11" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="CF11" t="n">
         <v>0</v>
@@ -5565,27 +5563,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H12" s="1" t="n">
@@ -5593,44 +5591,44 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Y5-16</t>
+          <t>W5-6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>00079393</t>
+          <t>00079412</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>30066-AY00- 640X200F-AGA0C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>30033-BY00- 640X200F-AGA0C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="Q12" t="n">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5645,7 +5643,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>00073552</t>
+          <t>00073568</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5655,7 +5653,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5670,16 +5668,16 @@
         <v>1</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AD12" s="1" t="n">
@@ -5688,15 +5686,13 @@
       <c r="AE12" s="1" t="n">
         <v>46169</v>
       </c>
-      <c r="AF12" s="1" t="n">
-        <v>46169</v>
-      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" s="1" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -5704,7 +5700,7 @@
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -5716,7 +5712,7 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -5839,13 +5835,13 @@
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="CE12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CF12" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="CG12" t="n">
         <v>0</v>
@@ -6011,27 +6007,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H13" s="1" t="n">
@@ -6039,44 +6035,44 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Y5-17</t>
+          <t>W5-7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>00079395</t>
+          <t>00079413</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>30040-AY00- 640X250F-A   C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>30020-BY00- 640X250F-A   C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="Q13" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -6091,7 +6087,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>00073553</t>
+          <t>00073569</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6101,7 +6097,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6116,11 +6112,11 @@
         <v>1</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6129,20 +6125,18 @@
         </is>
       </c>
       <c r="AD13" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="AE13" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="AF13" s="1" t="n">
-        <v>46170</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" s="1" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -6150,7 +6144,7 @@
         </is>
       </c>
       <c r="AK13" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -6162,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -6300,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="CJ13" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -6477,7 +6471,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H14" s="1" t="n">
@@ -6485,12 +6479,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>W5-5</t>
+          <t>W5-8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>00079411</t>
+          <t>00079414</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6537,7 +6531,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>00073567</t>
+          <t>00073570</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -6562,7 +6556,7 @@
         <v>1</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -6575,18 +6569,18 @@
         </is>
       </c>
       <c r="AD14" s="1" t="n">
-        <v>46164</v>
+        <v>46177</v>
       </c>
       <c r="AE14" s="1" t="n">
-        <v>46164</v>
+        <v>46177</v>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -6714,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -6723,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
@@ -6750,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
@@ -6921,20 +6915,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>W5-6</t>
+          <t>W5-10-2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>00079412</t>
+          <t>00079515</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6949,24 +6943,24 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>9000</v>
+        <v>250</v>
       </c>
       <c r="Q15" t="n">
-        <v>9000</v>
+        <v>250</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6981,12 +6975,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>00073568</t>
+          <t>00073680</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -7006,7 +7000,7 @@
         <v>1</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -7019,38 +7013,40 @@
         </is>
       </c>
       <c r="AD15" s="1" t="n">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="AE15" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
+        <v>46157</v>
+      </c>
+      <c r="AF15" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" s="1" t="n">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AO15" t="n">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -7149,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -7173,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
         <v>0</v>
@@ -7365,20 +7361,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>W5-7</t>
+          <t>W5-10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>00079413</t>
+          <t>00079468</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7393,24 +7389,24 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="Q16" t="n">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7425,12 +7421,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>00073569</t>
+          <t>00073606</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7450,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>46164</v>
+        <v>46153</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -7463,38 +7459,40 @@
         </is>
       </c>
       <c r="AD16" s="1" t="n">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="AE16" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>46157</v>
+      </c>
+      <c r="AF16" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" s="1" t="n">
-        <v>46167</v>
+        <v>46154</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>46167</v>
+        <v>46154</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
@@ -7593,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -7632,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="CI16" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="CJ16" t="n">
         <v>0</v>
@@ -7809,20 +7807,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46149</v>
+        <v>46135</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>W5-8</t>
+          <t>W5-2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>00079414</t>
+          <t>00079138</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7837,20 +7835,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="Q17" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -7869,12 +7867,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>00073570</t>
+          <t>00073324</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7894,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>46168</v>
+        <v>46153</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -7907,38 +7905,40 @@
         </is>
       </c>
       <c r="AD17" s="1" t="n">
-        <v>46177</v>
+        <v>46156</v>
       </c>
       <c r="AE17" s="1" t="n">
-        <v>46177</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>46156</v>
+      </c>
+      <c r="AF17" s="1" t="n">
+        <v>46160</v>
+      </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" s="1" t="n">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>46169</v>
+        <v>46154</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AO17" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
@@ -8034,10 +8034,10 @@
         <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -8082,7 +8082,7 @@
         <v>0</v>
       </c>
       <c r="CK17" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
@@ -8257,16 +8257,16 @@
         </is>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>W5-10-2</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>00079515</t>
+          <t>00079580</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8281,24 +8281,24 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>15025-SR28-1550X250F-ABK0J</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>15025-NR28-1550X250F-ABK0J</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="Q18" t="n">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>EC,巻返し,欠点表示</t>
+          <t>EC,巻返し</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>00073680</t>
+          <t>00073725</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -8338,7 +8338,7 @@
         <v>1</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -8351,40 +8351,40 @@
         </is>
       </c>
       <c r="AD18" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="AE18" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="AF18" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="AI18" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="AL18" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -8492,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8703,16 +8703,16 @@
         </is>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>W5-10</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>00079468</t>
+          <t>00079580</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8727,24 +8727,24 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>15025-SR28-1550X250F-ABK0J</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>15025-NR28-1550X250F-ABK0J</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="Q19" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>EC,巻返し,欠点表示</t>
+          <t>EC,巻返し</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8759,17 +8759,17 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>00073606</t>
+          <t>00073726</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8784,7 +8784,7 @@
         <v>1</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
@@ -8797,40 +8797,40 @@
         </is>
       </c>
       <c r="AD19" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="AE19" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="AF19" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="AI19" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="AL19" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
@@ -8929,7 +8929,7 @@
         <v>0</v>
       </c>
       <c r="BV19" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -9145,52 +9145,52 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46139</v>
+        <v>46135</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Y5-9</t>
+          <t>W5-3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>00079230</t>
+          <t>00079139</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>30040-AG00-1030X200F-ABK0C</t>
+          <t>15020-AX5R-1300X300F-A   P</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>30020-KG00-1030X200F-ABK0C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>400</v>
+        <v>4200</v>
       </c>
       <c r="Q20" t="n">
-        <v>800</v>
+        <v>4200</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>00073418</t>
+          <t>00073325</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -9230,7 +9230,7 @@
         <v>1</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
@@ -9243,40 +9243,40 @@
         </is>
       </c>
       <c r="AD20" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AE20" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>400</v>
+        <v>4200</v>
       </c>
       <c r="AL20" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="AM20" t="n">
-        <v>-400</v>
+        <v>3600</v>
       </c>
       <c r="AN20" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="AO20" t="n">
-        <v>400</v>
+        <v>4200</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
         <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -9571,72 +9571,72 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46135</v>
+        <v>46154</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>00079138</t>
+          <t>00079586</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15024-SRHW-1860X193F-A   B</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15024-SOFT-1600X 10F-A   B</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>6000</v>
+        <v>193</v>
       </c>
       <c r="Q21" t="n">
-        <v>6000</v>
+        <v>10</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,スリット</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9651,17 +9651,17 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>00073324</t>
+          <t>00073732</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9670,17 +9670,17 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
         <v>1</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -9689,20 +9689,18 @@
         </is>
       </c>
       <c r="AD21" s="1" t="n">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="AE21" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="AF21" s="1" t="n">
-        <v>46160</v>
-      </c>
+        <v>46161</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" s="1" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -9710,19 +9708,19 @@
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>6000</v>
+        <v>10</v>
       </c>
       <c r="AL21" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>6000</v>
+        <v>10</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
@@ -9818,16 +9816,16 @@
         <v>0</v>
       </c>
       <c r="BU21" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="BV21" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BY21" t="n">
         <v>0</v>
@@ -10017,72 +10015,72 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46135</v>
+        <v>46154</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>00079139</t>
+          <t>00079586</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15024-SRHW-1860X193F-A   B</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15024-SOFT-1600X 10F-A   B</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4200</v>
+        <v>193</v>
       </c>
       <c r="Q22" t="n">
-        <v>4200</v>
+        <v>10</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,スリット</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10097,7 +10095,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>00073325</t>
+          <t>00073731</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10107,7 +10105,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10116,17 +10114,17 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="n">
         <v>1</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10135,20 +10133,18 @@
         </is>
       </c>
       <c r="AD22" s="1" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="AE22" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="AF22" s="1" t="n">
-        <v>46162</v>
-      </c>
+        <v>46161</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -10156,19 +10152,19 @@
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>4200</v>
+        <v>193</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>4200</v>
+        <v>193</v>
       </c>
       <c r="AP22" t="n">
         <v>0</v>
@@ -10267,13 +10263,13 @@
         <v>0</v>
       </c>
       <c r="BV22" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="BW22" t="n">
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="BY22" t="n">
         <v>0</v>
@@ -10483,7 +10479,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H23" s="1" t="n">
@@ -10491,12 +10487,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Y5-31</t>
+          <t>Y5-33</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>00079542</t>
+          <t>00079545</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10511,20 +10507,20 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-A   C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 820X200F-A   C</t>
+          <t>0R040-8Y0B- 260X200H-ABG1C</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="Q23" t="n">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -10543,7 +10539,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>00073696</t>
+          <t>00073699</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -10581,18 +10577,20 @@
         </is>
       </c>
       <c r="AD23" s="1" t="n">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="AE23" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
+        <v>46157</v>
+      </c>
+      <c r="AF23" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" s="1" t="n">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -10600,7 +10598,7 @@
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -10612,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -10714,7 +10712,7 @@
         <v>0</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="BX23" t="n">
         <v>0</v>
@@ -10729,7 +10727,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -10917,30 +10915,30 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>017</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46154</v>
+        <v>46135</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Y5-32</t>
+          <t>V5-1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>00079543</t>
+          <t>00079141</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10955,24 +10953,24 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 830X200F-ABG1C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1400</v>
+        <v>8600</v>
       </c>
       <c r="Q24" t="n">
-        <v>2800</v>
+        <v>8600</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -10987,17 +10985,17 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>00073697</t>
+          <t>00073323</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11012,7 +11010,7 @@
         <v>1</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
@@ -11025,18 +11023,20 @@
         </is>
       </c>
       <c r="AD24" s="1" t="n">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="AE24" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
+        <v>46157</v>
+      </c>
+      <c r="AF24" s="1" t="n">
+        <v>46157</v>
+      </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" s="1" t="n">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -11044,19 +11044,19 @@
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>1400</v>
+        <v>8600</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="AO24" t="n">
-        <v>1400</v>
+        <v>8600</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
@@ -11155,10 +11155,10 @@
         <v>0</v>
       </c>
       <c r="BV24" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="BW24" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="BX24" t="n">
         <v>0</v>
@@ -11173,7 +11173,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="CC24" t="n">
         <v>0</v>
@@ -11361,62 +11361,62 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Y5-29</t>
+          <t>W5-10-2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>00079478</t>
+          <t>00079515</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-ABK0C</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-ABK0C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4000</v>
+        <v>250</v>
       </c>
       <c r="Q25" t="n">
-        <v>4000</v>
+        <v>250</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>00073652</t>
+          <t>00073681</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -11460,29 +11460,29 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AD25" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="AE25" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -11490,19 +11490,19 @@
         </is>
       </c>
       <c r="AK25" t="n">
-        <v>4000</v>
+        <v>250</v>
       </c>
       <c r="AL25" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>4000</v>
+        <v>250</v>
       </c>
       <c r="AP25" t="n">
         <v>0</v>
@@ -11601,10 +11601,10 @@
         <v>0</v>
       </c>
       <c r="BV25" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="BX25" t="n">
         <v>0</v>
@@ -11807,62 +11807,62 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Y5-33</t>
+          <t>W5-10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>00079545</t>
+          <t>00079468</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 260X200H-ABG1C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="Q26" t="n">
-        <v>2400</v>
+        <v>500</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>00073699</t>
+          <t>00073608</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11902,16 +11902,16 @@
         <v>1</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AD26" s="1" t="n">
@@ -11936,7 +11936,7 @@
         </is>
       </c>
       <c r="AK26" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -11948,7 +11948,7 @@
         <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="AP26" t="n">
         <v>0</v>
@@ -12050,7 +12050,7 @@
         <v>0</v>
       </c>
       <c r="BW26" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="BX26" t="n">
         <v>0</v>
@@ -12253,62 +12253,62 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46135</v>
+        <v>46153</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>V5-1</t>
+          <t>W5-10-2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>00079141</t>
+          <t>00079515</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>8600</v>
+        <v>250</v>
       </c>
       <c r="Q27" t="n">
-        <v>8600</v>
+        <v>250</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC,巻返し,欠点表示</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>00073323</t>
+          <t>00073682</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="AI27" s="1" t="n">
         <v>46155</v>
@@ -12382,7 +12382,7 @@
         </is>
       </c>
       <c r="AK27" t="n">
-        <v>8600</v>
+        <v>250</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -12394,7 +12394,7 @@
         <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>8600</v>
+        <v>250</v>
       </c>
       <c r="AP27" t="n">
         <v>0</v>
@@ -12493,10 +12493,10 @@
         <v>0</v>
       </c>
       <c r="BV27" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BW27" t="n">
-        <v>4600</v>
+        <v>250</v>
       </c>
       <c r="BX27" t="n">
         <v>0</v>
@@ -12699,30 +12699,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>012</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>W5-10-2</t>
+          <t>W5-10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>00079515</t>
+          <t>00079468</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12747,10 +12747,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="Q28" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>00073681</t>
+          <t>00073609</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="AK28" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -12840,7 +12840,7 @@
         <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AP28" t="n">
         <v>0</v>
@@ -12942,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="BW28" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="BX28" t="n">
         <v>0</v>
@@ -13155,52 +13155,52 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>W5-10</t>
+          <t>V5-4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>00079468</t>
+          <t>00079421</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>30040-AY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>30020-BY00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="Q29" t="n">
-        <v>500</v>
+        <v>8000</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>EC,巻返し,欠点表示</t>
+          <t>スライス,巻返し</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>00073608</t>
+          <t>00073580</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -13244,29 +13244,29 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD29" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AE29" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         </is>
       </c>
       <c r="AK29" t="n">
-        <v>500</v>
+        <v>8000</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -13286,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>500</v>
+        <v>8000</v>
       </c>
       <c r="AP29" t="n">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="BW29" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="BY29" t="n">
         <v>0</v>
@@ -13591,62 +13591,62 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>011</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>W5-10-2</t>
+          <t>Y5-18</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>00079515</t>
+          <t>00079396</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>30040-AY00- 960X250F-A   C</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>30020-BY00- 450X250F-A   C</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="Q30" t="n">
-        <v>250</v>
+        <v>12000</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>EC,巻返し,欠点表示</t>
+          <t>スリット,スライス</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>00073682</t>
+          <t>00073554</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13686,11 +13686,11 @@
         <v>1</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -13699,20 +13699,20 @@
         </is>
       </c>
       <c r="AD30" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AE30" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -13732,7 +13732,7 @@
         <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="AP30" t="n">
         <v>0</v>
@@ -13834,13 +13834,13 @@
         <v>0</v>
       </c>
       <c r="BW30" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="BX30" t="n">
         <v>0</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -14037,30 +14037,30 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>016</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>W5-10</t>
+          <t>Y5-19</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>00079468</t>
+          <t>00079397</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -14075,24 +14075,24 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="Q31" t="n">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>EC,巻返し,欠点表示</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>00073609</t>
+          <t>00073556</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -14132,11 +14132,11 @@
         <v>1</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -14145,20 +14145,20 @@
         </is>
       </c>
       <c r="AD31" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AE31" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="AK31" t="n">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
         <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="AP31" t="n">
         <v>0</v>
@@ -14280,13 +14280,13 @@
         <v>0</v>
       </c>
       <c r="BW31" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="BX31" t="n">
         <v>0</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="BZ31" t="n">
         <v>0</v>
@@ -14483,17 +14483,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>015</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
@@ -14501,44 +14501,44 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>V5-4</t>
+          <t>Y5-19</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>00079421</t>
+          <t>00079397</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>30040-AY00-1000X200F-A   C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>30020-BY00-1000X200F-A   C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="Q32" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>スライス,巻返し</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>00073580</t>
+          <t>00073555</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -14578,33 +14578,33 @@
         <v>1</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AD32" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="AE32" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="AF32" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         </is>
       </c>
       <c r="AK32" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="AP32" t="n">
         <v>0</v>
@@ -14729,10 +14729,10 @@
         <v>0</v>
       </c>
       <c r="BX32" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="BZ32" t="n">
         <v>0</v>
@@ -14939,20 +14939,20 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>013</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Y5-18</t>
+          <t>Y5-32</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>00079396</t>
+          <t>00079543</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14967,24 +14967,24 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>30040-AY00- 960X250F-A   C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>30020-BY00- 450X250F-A   C</t>
+          <t>0R040-8Y0B- 830X200F-ABG1C</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="Q33" t="n">
-        <v>12000</v>
+        <v>2800</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>スリット,スライス</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>00073554</t>
+          <t>00073697</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -15024,7 +15024,7 @@
         <v>1</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -15037,20 +15037,20 @@
         </is>
       </c>
       <c r="AD33" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="AE33" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="AK33" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -15070,7 +15070,7 @@
         <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="AP33" t="n">
         <v>0</v>
@@ -15178,7 +15178,7 @@
         <v>0</v>
       </c>
       <c r="BY33" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -15187,7 +15187,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -15385,52 +15385,52 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Y5-19</t>
+          <t>Y5-31</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>00079397</t>
+          <t>00079542</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>0R040-8Y0B- 870X200F-A   C</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="Q34" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>00073556</t>
+          <t>00073696</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -15470,7 +15470,7 @@
         <v>1</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -15479,24 +15479,24 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD34" s="1" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="AE34" s="1" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         </is>
       </c>
       <c r="AK34" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -15516,7 +15516,7 @@
         <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AP34" t="n">
         <v>0</v>
@@ -15624,7 +15624,7 @@
         <v>0</v>
       </c>
       <c r="BY34" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -15821,12 +15821,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -15835,63 +15835,63 @@
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Y5-19</t>
+          <t>JR260502</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>00079397</t>
+          <t>00079577</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t xml:space="preserve">7A1 </t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t xml:space="preserve">0   </t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>40040-R10W- 870X 95</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="Q35" t="n">
-        <v>6000</v>
+        <v>760</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>東レ株式会社</t>
+          <t>東レペフ加工品株式会社</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>自動車材料事業部</t>
+          <t>(国分・湖南用)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>00073555</t>
+          <t>00073724</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Y35" t="n">
@@ -15916,33 +15916,33 @@
         <v>1</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD35" s="1" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="AE35" s="1" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="AF35" s="1" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="AI35" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         </is>
       </c>
       <c r="AK35" t="n">
-        <v>6000</v>
+        <v>760</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -15962,7 +15962,7 @@
         <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>6000</v>
+        <v>760</v>
       </c>
       <c r="AP35" t="n">
         <v>0</v>
@@ -16070,7 +16070,7 @@
         <v>0</v>
       </c>
       <c r="BY35" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="BZ35" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
         <v>0</v>
       </c>
       <c r="CC35" t="n">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="CD35" t="n">
         <v>0</v>
@@ -16267,77 +16267,77 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>JR260502</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>00079398</t>
+          <t>00079577</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t xml:space="preserve">7A1 </t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t xml:space="preserve">0   </t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>40040-R10W- 870X 95</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="Q36" t="n">
-        <v>12000</v>
+        <v>760</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>東レ株式会社</t>
+          <t>東レペフ加工品株式会社</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>自動車材料事業部</t>
+          <t>(国分・湖南用)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>00073558</t>
+          <t>00073723</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -16347,12 +16347,12 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Y36" t="n">
@@ -16362,33 +16362,33 @@
         <v>1</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD36" s="1" t="n">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="AE36" s="1" t="n">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="AF36" s="1" t="n">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" s="1" t="n">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="AI36" s="1" t="n">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="AK36" t="n">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -16408,7 +16408,7 @@
         <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="AP36" t="n">
         <v>0</v>
@@ -16528,7 +16528,7 @@
         <v>0</v>
       </c>
       <c r="CC36" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CD36" t="n">
         <v>0</v>
@@ -16552,10 +16552,10 @@
         <v>0</v>
       </c>
       <c r="CK36" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="CL36" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="CM36" t="n">
         <v>0</v>
@@ -16713,17 +16713,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>014</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>00073557</t>
+          <t>00073558</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AK37" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -16854,7 +16854,7 @@
         <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="AP37" t="n">
         <v>0</v>
@@ -16998,10 +16998,10 @@
         <v>0</v>
       </c>
       <c r="CK37" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="CL37" t="n">
-        <v>9000</v>
+        <v>4500</v>
       </c>
       <c r="CM37" t="n">
         <v>0</v>
@@ -17149,72 +17149,72 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Y5-32</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>00079543</t>
+          <t>00079398</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 830X200F-ABG1C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1400</v>
+        <v>6000</v>
       </c>
       <c r="Q38" t="n">
-        <v>2800</v>
+        <v>12000</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>スリット,SEC</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -17229,7 +17229,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>00073698</t>
+          <t>00073557</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -17254,7 +17254,7 @@
         <v>1</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
@@ -17267,18 +17267,20 @@
         </is>
       </c>
       <c r="AD38" s="1" t="n">
-        <v>46163</v>
+        <v>46171</v>
       </c>
       <c r="AE38" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>46171</v>
+      </c>
+      <c r="AF38" s="1" t="n">
+        <v>46171</v>
+      </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" s="1" t="n">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>46161</v>
+        <v>46170</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -17286,7 +17288,7 @@
         </is>
       </c>
       <c r="AK38" t="n">
-        <v>1400</v>
+        <v>12000</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -17298,7 +17300,7 @@
         <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1400</v>
+        <v>12000</v>
       </c>
       <c r="AP38" t="n">
         <v>0</v>
@@ -17418,7 +17420,7 @@
         <v>0</v>
       </c>
       <c r="CC38" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="CD38" t="n">
         <v>0</v>
@@ -17442,10 +17444,10 @@
         <v>0</v>
       </c>
       <c r="CK38" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="CL38" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="CM38" t="n">
         <v>0</v>
@@ -17613,20 +17615,20 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Y5-25</t>
+          <t>Y5-34</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>00079403</t>
+          <t>00079583</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -17641,20 +17643,20 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22044-AA00-1050X210F-A   C</t>
+          <t>50080-AY0B- 680X200F-A   C</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>22022-8A00-1050X210F-A   C</t>
+          <t>0R040-8Y0B- 680X200F-A   C</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>6300</v>
+        <v>3000</v>
       </c>
       <c r="Q39" t="n">
-        <v>12600</v>
+        <v>6000</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -17673,7 +17675,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>00073563</t>
+          <t>00073728</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -17698,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -17707,24 +17709,22 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD39" s="1" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="AE39" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="AF39" s="1" t="n">
-        <v>46163</v>
-      </c>
+        <v>46170</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" s="1" t="n">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         </is>
       </c>
       <c r="AK39" t="n">
-        <v>6300</v>
+        <v>3000</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -17744,7 +17744,7 @@
         <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>6300</v>
+        <v>3000</v>
       </c>
       <c r="AP39" t="n">
         <v>0</v>
@@ -17864,7 +17864,7 @@
         <v>0</v>
       </c>
       <c r="CC39" t="n">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="CD39" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0</v>
       </c>
       <c r="CK39" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="CL39" t="n">
         <v>0</v>
@@ -18063,16 +18063,16 @@
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Y5-21</t>
+          <t>Y5-32</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>00079399</t>
+          <t>00079543</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -18087,24 +18087,24 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 830X200F-ABG1C</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>9000</v>
+        <v>1400</v>
       </c>
       <c r="Q40" t="n">
-        <v>18000</v>
+        <v>2800</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット,SEC</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>00073559</t>
+          <t>00073698</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -18138,7 +18138,7 @@
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -18157,13 +18157,13 @@
         </is>
       </c>
       <c r="AD40" s="1" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="AE40" s="1" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" s="1" t="n">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="AK40" t="n">
-        <v>9000</v>
+        <v>1400</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>9000</v>
+        <v>1400</v>
       </c>
       <c r="AP40" t="n">
         <v>0</v>
@@ -18313,7 +18313,7 @@
         <v>0</v>
       </c>
       <c r="CD40" t="n">
-        <v>9000</v>
+        <v>1400</v>
       </c>
       <c r="CE40" t="n">
         <v>0</v>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
@@ -18513,12 +18513,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Y5-23</t>
+          <t>Y5-25</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>00079401</t>
+          <t>00079403</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -18533,20 +18533,20 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>22044-AA00-1050X210F-A   C</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>22022-8A00-1050X210F-A   C</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>9000</v>
+        <v>6300</v>
       </c>
       <c r="Q41" t="n">
-        <v>18000</v>
+        <v>12600</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>00073561</t>
+          <t>00073563</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -18590,7 +18590,7 @@
         <v>1</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
@@ -18603,20 +18603,20 @@
         </is>
       </c>
       <c r="AD41" s="1" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="AE41" s="1" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="AF41" s="1" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" s="1" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="AI41" s="1" t="n">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         </is>
       </c>
       <c r="AK41" t="n">
-        <v>9000</v>
+        <v>6300</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -18636,7 +18636,7 @@
         <v>0</v>
       </c>
       <c r="AO41" t="n">
-        <v>9000</v>
+        <v>6300</v>
       </c>
       <c r="AP41" t="n">
         <v>0</v>
@@ -18756,13 +18756,13 @@
         <v>0</v>
       </c>
       <c r="CC41" t="n">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="CD41" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CE41" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="CF41" t="n">
         <v>0</v>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Y5-22</t>
+          <t>Y5-21</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>00079400</t>
+          <t>00079399</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>00073560</t>
+          <t>00073559</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -19036,7 +19036,7 @@
         <v>1</v>
       </c>
       <c r="AA42" s="1" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
@@ -19049,20 +19049,20 @@
         </is>
       </c>
       <c r="AD42" s="1" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="AE42" s="1" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="AF42" s="1" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="AI42" s="1" t="n">
         <v>46163</v>
-      </c>
-      <c r="AI42" s="1" t="n">
-        <v>46164</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -19205,13 +19205,13 @@
         <v>0</v>
       </c>
       <c r="CD42" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="CE42" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="CF42" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="CG42" t="n">
         <v>0</v>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
@@ -19405,12 +19405,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Y5-27</t>
+          <t>Y5-23</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>00079405</t>
+          <t>00079401</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -19425,13 +19425,13 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>00073565</t>
+          <t>00073561</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -19476,13 +19476,13 @@
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
@@ -19495,20 +19495,20 @@
         </is>
       </c>
       <c r="AD43" s="1" t="n">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="AE43" s="1" t="n">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" s="1" t="n">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>0</v>
       </c>
       <c r="CE43" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="CF43" t="n">
         <v>0</v>
@@ -19666,7 +19666,7 @@
         <v>0</v>
       </c>
       <c r="CI43" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="CJ43" t="n">
         <v>0</v>
@@ -19843,67 +19843,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Y5-24</t>
+          <t>JR260502</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>00079402</t>
+          <t>00079577</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t xml:space="preserve">7A1 </t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t xml:space="preserve">0   </t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>40040-R10W- 870X 95</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>9000</v>
+        <v>800</v>
       </c>
       <c r="Q44" t="n">
-        <v>18000</v>
+        <v>760</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>東レ株式会社</t>
+          <t>東レペフ加工品株式会社</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>自動車材料事業部</t>
+          <t>(国分・湖南用)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>00073562</t>
+          <t>00073722</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Y44" t="n">
@@ -19928,7 +19928,7 @@
         <v>1</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
@@ -19937,24 +19937,24 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD44" s="1" t="n">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="AE44" s="1" t="n">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" s="1" t="n">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         </is>
       </c>
       <c r="AK44" t="n">
-        <v>9000</v>
+        <v>800</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -19974,7 +19974,7 @@
         <v>0</v>
       </c>
       <c r="AO44" t="n">
-        <v>9000</v>
+        <v>800</v>
       </c>
       <c r="AP44" t="n">
         <v>0</v>
@@ -20094,7 +20094,7 @@
         <v>0</v>
       </c>
       <c r="CC44" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CD44" t="n">
         <v>0</v>
@@ -20115,7 +20115,7 @@
         <v>0</v>
       </c>
       <c r="CJ44" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="CK44" t="n">
         <v>0</v>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
@@ -20297,12 +20297,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Y5-26</t>
+          <t>Y5-22</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>00079404</t>
+          <t>00079400</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -20317,20 +20317,20 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="Q45" t="n">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>00073564</t>
+          <t>00073560</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -20368,13 +20368,13 @@
         </is>
       </c>
       <c r="Y45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -20387,20 +20387,20 @@
         </is>
       </c>
       <c r="AD45" s="1" t="n">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="AE45" s="1" t="n">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" s="1" t="n">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -20420,7 +20420,7 @@
         <v>0</v>
       </c>
       <c r="AO45" t="n">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="AP45" t="n">
         <v>0</v>
@@ -20549,7 +20549,7 @@
         <v>0</v>
       </c>
       <c r="CF45" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="CG45" t="n">
         <v>0</v>
@@ -20567,7 +20567,7 @@
         <v>0</v>
       </c>
       <c r="CL45" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="CM45" t="n">
         <v>0</v>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>010</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
@@ -20743,12 +20743,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Y5-28</t>
+          <t>Y5-27</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>00079408</t>
+          <t>00079405</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -20763,13 +20763,13 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>50080-AY0B- 870X200F-AGA1C</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -20795,7 +20795,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>00073566</t>
+          <t>00073565</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -20814,13 +20814,13 @@
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="n">
         <v>1</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
@@ -20833,20 +20833,20 @@
         </is>
       </c>
       <c r="AD46" s="1" t="n">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="AE46" s="1" t="n">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" s="1" t="n">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>0</v>
       </c>
       <c r="CF46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CG46" t="n">
         <v>0</v>
@@ -21004,13 +21004,13 @@
         <v>0</v>
       </c>
       <c r="CI46" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="CJ46" t="n">
         <v>0</v>
       </c>
       <c r="CK46" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="CL46" t="n">
         <v>0</v>
@@ -21161,40 +21161,40 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Y5-10</t>
+          <t>Y5-24</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>00079232</t>
+          <t>00079402</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -21209,24 +21209,24 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3600</v>
+        <v>9000</v>
       </c>
       <c r="Q47" t="n">
-        <v>3600</v>
+        <v>18000</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>00073416</t>
+          <t>00073562</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -21251,7 +21251,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -21266,33 +21266,33 @@
         <v>1</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AD47" s="1" t="n">
-        <v>46162</v>
+        <v>46170</v>
       </c>
       <c r="AE47" s="1" t="n">
-        <v>46162</v>
+        <v>46170</v>
       </c>
       <c r="AF47" s="1" t="n">
-        <v>46162</v>
+        <v>46170</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" s="1" t="n">
-        <v>46156</v>
+        <v>46167</v>
       </c>
       <c r="AI47" s="1" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="AK47" t="n">
-        <v>3600</v>
+        <v>9000</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -21312,7 +21312,7 @@
         <v>0</v>
       </c>
       <c r="AO47" t="n">
-        <v>3600</v>
+        <v>9000</v>
       </c>
       <c r="AP47" t="n">
         <v>0</v>
@@ -21417,7 +21417,7 @@
         <v>0</v>
       </c>
       <c r="BX47" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="BY47" t="n">
         <v>0</v>
@@ -21450,10 +21450,10 @@
         <v>0</v>
       </c>
       <c r="CI47" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CJ47" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="CK47" t="n">
         <v>0</v>
@@ -21607,40 +21607,40 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0015</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Y5-10</t>
+          <t>Y5-26</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>00079232</t>
+          <t>00079404</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -21655,24 +21655,24 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>25020-AG00- 750X400F-AGR0C</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3600</v>
+        <v>7000</v>
       </c>
       <c r="Q48" t="n">
-        <v>3600</v>
+        <v>14000</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>分割,エンボス</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -21687,7 +21687,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>00073417</t>
+          <t>00073564</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -21697,7 +21697,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>0015</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -21712,33 +21712,33 @@
         <v>1</v>
       </c>
       <c r="AA48" s="1" t="n">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AD48" s="1" t="n">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="AE48" s="1" t="n">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" s="1" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>3600</v>
+        <v>7000</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
         <v>0</v>
       </c>
       <c r="AO48" t="n">
-        <v>3600</v>
+        <v>7000</v>
       </c>
       <c r="AP48" t="n">
         <v>0</v>
@@ -21863,7 +21863,7 @@
         <v>0</v>
       </c>
       <c r="BX48" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="BY48" t="n">
         <v>0</v>
@@ -21905,7 +21905,7 @@
         <v>0</v>
       </c>
       <c r="CL48" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="CM48" t="n">
         <v>0</v>
@@ -22053,27 +22053,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>011</t>
         </is>
       </c>
       <c r="H49" s="1" t="n">
@@ -22081,44 +22081,44 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>W5-5</t>
+          <t>Y5-28</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>00079411</t>
+          <t>00079408</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>50080-AY0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="P49" t="n">
         <v>9000</v>
       </c>
       <c r="Q49" t="n">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>00073571</t>
+          <t>00073566</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -22158,11 +22158,11 @@
         <v>1</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>46157</v>
+        <v>46167</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -22171,18 +22171,20 @@
         </is>
       </c>
       <c r="AD49" s="1" t="n">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="AE49" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
+        <v>46171</v>
+      </c>
+      <c r="AF49" s="1" t="n">
+        <v>46171</v>
+      </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" s="1" t="n">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="AI49" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -22319,34 +22321,34 @@
         <v>0</v>
       </c>
       <c r="CB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ49" t="n">
         <v>3000</v>
       </c>
-      <c r="CC49" t="n">
-        <v>3900</v>
-      </c>
-      <c r="CD49" t="n">
-        <v>2100</v>
-      </c>
-      <c r="CE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ49" t="n">
-        <v>0</v>
-      </c>
       <c r="CK49" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="CL49" t="n">
         <v>0</v>
@@ -22497,72 +22499,72 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46149</v>
+        <v>46139</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>W5-6</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>00079412</t>
+          <t>00079232</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="Q50" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -22577,7 +22579,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>00073572</t>
+          <t>00073416</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -22587,7 +22589,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -22602,31 +22604,33 @@
         <v>1</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD50" s="1" t="n">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="AE50" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
+        <v>46162</v>
+      </c>
+      <c r="AF50" s="1" t="n">
+        <v>46162</v>
+      </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" s="1" t="n">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -22634,7 +22638,7 @@
         </is>
       </c>
       <c r="AK50" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -22646,7 +22650,7 @@
         <v>0</v>
       </c>
       <c r="AO50" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="AP50" t="n">
         <v>0</v>
@@ -22751,7 +22755,7 @@
         <v>0</v>
       </c>
       <c r="BX50" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="BY50" t="n">
         <v>0</v>
@@ -22769,7 +22773,7 @@
         <v>0</v>
       </c>
       <c r="CD50" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="CE50" t="n">
         <v>0</v>
@@ -22784,10 +22788,10 @@
         <v>0</v>
       </c>
       <c r="CI50" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="CJ50" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="CK50" t="n">
         <v>0</v>
@@ -22941,72 +22945,72 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>0015</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46149</v>
+        <v>46139</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>W5-7</t>
+          <t>Y5-10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>00079413</t>
+          <t>00079232</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>25020-AG00- 750X400F-AGR0C</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="Q51" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>分割,エンボス</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -23021,7 +23025,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>00073573</t>
+          <t>00073417</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -23031,7 +23035,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>0015</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -23046,31 +23050,33 @@
         <v>1</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AD51" s="1" t="n">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="AE51" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
+        <v>46162</v>
+      </c>
+      <c r="AF51" s="1" t="n">
+        <v>46162</v>
+      </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" s="1" t="n">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>46171</v>
+        <v>46156</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -23078,7 +23084,7 @@
         </is>
       </c>
       <c r="AK51" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -23090,7 +23096,7 @@
         <v>0</v>
       </c>
       <c r="AO51" t="n">
-        <v>9000</v>
+        <v>3600</v>
       </c>
       <c r="AP51" t="n">
         <v>0</v>
@@ -23195,7 +23201,7 @@
         <v>0</v>
       </c>
       <c r="BX51" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="BY51" t="n">
         <v>0</v>
@@ -23231,16 +23237,16 @@
         <v>0</v>
       </c>
       <c r="CJ51" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="CK51" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="CL51" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="CM51" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
@@ -23405,7 +23411,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
@@ -23413,12 +23419,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>W5-8</t>
+          <t>W5-5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>00079414</t>
+          <t>00079411</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -23465,7 +23471,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>00073574</t>
+          <t>00073571</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -23490,7 +23496,7 @@
         <v>1</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
@@ -23503,18 +23509,18 @@
         </is>
       </c>
       <c r="AD52" s="1" t="n">
-        <v>46177</v>
+        <v>46164</v>
       </c>
       <c r="AE52" s="1" t="n">
-        <v>46177</v>
+        <v>46164</v>
       </c>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" s="1" t="n">
-        <v>46174</v>
+        <v>46160</v>
       </c>
       <c r="AI52" s="1" t="n">
-        <v>46176</v>
+        <v>46162</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -23651,13 +23657,13 @@
         <v>0</v>
       </c>
       <c r="CB52" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="CC52" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="CD52" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="CE52" t="n">
         <v>0</v>
@@ -23693,13 +23699,13 @@
         <v>0</v>
       </c>
       <c r="CP52" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="CQ52" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="CR52" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CS52" t="n">
         <v>0</v>
@@ -23853,16 +23859,16 @@
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>W5-2</t>
+          <t>W5-6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>00079138</t>
+          <t>00079412</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -23877,20 +23883,20 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="Q53" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -23909,7 +23915,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>00073327</t>
+          <t>00073572</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -23934,7 +23940,7 @@
         <v>1</v>
       </c>
       <c r="AA53" s="1" t="n">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -23947,20 +23953,18 @@
         </is>
       </c>
       <c r="AD53" s="1" t="n">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="AE53" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="AF53" s="1" t="n">
-        <v>46160</v>
-      </c>
+        <v>46169</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" s="1" t="n">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -23968,19 +23972,19 @@
         </is>
       </c>
       <c r="AK53" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="AL53" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="AP53" t="n">
         <v>0</v>
@@ -24079,10 +24083,10 @@
         <v>0</v>
       </c>
       <c r="BV53" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BW53" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BX53" t="n">
         <v>0</v>
@@ -24103,7 +24107,7 @@
         <v>0</v>
       </c>
       <c r="CD53" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="CE53" t="n">
         <v>0</v>
@@ -24118,10 +24122,10 @@
         <v>0</v>
       </c>
       <c r="CI53" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="CJ53" t="n">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="CK53" t="n">
         <v>0</v>
@@ -24295,20 +24299,20 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>W5-3</t>
+          <t>W5-7</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>00079139</t>
+          <t>00079413</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -24323,20 +24327,20 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>15020-AX5R-1300X300F-A   P</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>4200</v>
+        <v>9000</v>
       </c>
       <c r="Q54" t="n">
-        <v>4200</v>
+        <v>9000</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -24355,7 +24359,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>00073328</t>
+          <t>00073573</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -24380,7 +24384,7 @@
         <v>1</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -24393,318 +24397,1652 @@
         </is>
       </c>
       <c r="AD54" s="1" t="n">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="AE54" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="AF54" s="1" t="n">
-        <v>46162</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="AI54" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ54" t="n">
+        <v>600</v>
+      </c>
+      <c r="CK54" t="n">
+        <v>3900</v>
+      </c>
+      <c r="CL54" t="n">
+        <v>3900</v>
+      </c>
+      <c r="CM54" t="n">
+        <v>600</v>
+      </c>
+      <c r="CN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>520201</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>湖南工場01本倉庫</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0019</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>W5-8</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>00079414</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1440X300F-A   P</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1440X300F-A   R</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>9000</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>9000</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>東レ株式会社</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>自動車材料事業部</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>00073574</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>0019</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Y55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="AD55" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="AE55" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="AI55" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AK55" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP55" t="n">
+        <v>3900</v>
+      </c>
+      <c r="CQ55" t="n">
+        <v>3900</v>
+      </c>
+      <c r="CR55" t="n">
+        <v>1200</v>
+      </c>
+      <c r="CS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>520201</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>湖南工場01本倉庫</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0019</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>W5-2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>00079138</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1300X300F-A   P</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1300X300F-A   R</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>東レ株式会社</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>自動車材料事業部</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>00073327</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>1:完了</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>0019</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Y56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="AD56" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="AE56" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="AF56" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="AI56" s="1" t="n">
         <v>46155</v>
       </c>
-      <c r="AI54" s="1" t="n">
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="AK56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>3900</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>3900</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>3900</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>2100</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>520201</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>湖南工場01本倉庫</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0019</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>検査</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>W5-3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>00079139</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>15020-AX5R-1300X300F-A   P</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>15020-JX5R-1300X300F-A   R</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>4200</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4200</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>東レ株式会社</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>自動車材料事業部</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>00073328</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0:未完</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>0019</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>EC機　湖南</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S </t>
+        </is>
+      </c>
+      <c r="AD57" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="AE57" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="AF57" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="AI57" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AJ57" t="inlineStr">
         <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="AK54" t="n">
+      <c r="AK57" t="n">
         <v>4200</v>
       </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO54" t="n">
+      <c r="AL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="n">
         <v>4200</v>
       </c>
-      <c r="AP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW54" t="n">
-        <v>600</v>
-      </c>
-      <c r="BX54" t="n">
-        <v>3600</v>
-      </c>
-      <c r="BY54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED54" t="n">
+      <c r="AP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED57" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/stage1_task_input_table.xlsx
+++ b/output/stage1_task_input_table.xlsx
@@ -648,457 +648,457 @@
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>2026/04/25</t>
+          <t>2026/04/26</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>2026/04/26</t>
+          <t>2026/04/27</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>2026/04/27</t>
+          <t>2026/04/28</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>2026/04/28</t>
+          <t>2026/04/29</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>2026/04/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/02</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>2026/05/02</t>
+          <t>2026/05/03</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>2026/05/03</t>
+          <t>2026/05/04</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>2026/05/04</t>
+          <t>2026/05/05</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>2026/05/05</t>
+          <t>2026/05/06</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>2026/05/06</t>
+          <t>2026/05/07</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>2026/05/09</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>2026/05/10</t>
+          <t>2026/05/11</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/05/12</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>2026/05/12</t>
+          <t>2026/05/13</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>2026/05/13</t>
+          <t>2026/05/14</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/05/16</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>2026/05/16</t>
+          <t>2026/05/17</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>2026/05/17</t>
+          <t>2026/05/18</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/21</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>2026/05/21</t>
+          <t>2026/05/22</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/23</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>2026/05/23</t>
+          <t>2026/05/24</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>2026/05/24</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/05/27</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>2026/05/27</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/05/31</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>2026/05/31</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/03</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>2026/06/03</t>
+          <t>2026/06/04</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>2026/06/04</t>
+          <t>2026/06/05</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>2026/06/05</t>
+          <t>2026/06/06</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>2026/06/06</t>
+          <t>2026/06/07</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>2026/06/07</t>
+          <t>2026/06/08</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>2026/06/08</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/06/10</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>2026/06/10</t>
+          <t>2026/06/11</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>2026/06/11</t>
+          <t>2026/06/12</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>2026/06/12</t>
+          <t>2026/06/13</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>2026/06/13</t>
+          <t>2026/06/14</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>2026/06/14</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/16</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/17</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>2026/06/17</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/06/20</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>2026/06/20</t>
+          <t>2026/06/21</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>2026/06/21</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/23</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>2026/06/23</t>
+          <t>2026/06/24</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/06/27</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
-          <t>2026/06/30</t>
+          <t>2026/07/01</t>
         </is>
       </c>
       <c r="DI1" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/02</t>
         </is>
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/07/03</t>
         </is>
       </c>
       <c r="DK1" t="inlineStr">
         <is>
-          <t>2026/07/03</t>
+          <t>2026/07/04</t>
         </is>
       </c>
       <c r="DL1" t="inlineStr">
         <is>
-          <t>2026/07/04</t>
+          <t>2026/07/05</t>
         </is>
       </c>
       <c r="DM1" t="inlineStr">
         <is>
-          <t>2026/07/05</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="DN1" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="DO1" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="DP1" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/09</t>
         </is>
       </c>
       <c r="DQ1" t="inlineStr">
         <is>
-          <t>2026/07/09</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="DR1" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/11</t>
         </is>
       </c>
       <c r="DS1" t="inlineStr">
         <is>
-          <t>2026/07/11</t>
+          <t>2026/07/12</t>
         </is>
       </c>
       <c r="DT1" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="DU1" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="DV1" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/15</t>
         </is>
       </c>
       <c r="DW1" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="DX1" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="DY1" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="DZ1" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/19</t>
         </is>
       </c>
       <c r="EA1" t="inlineStr">
         <is>
-          <t>2026/07/19</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="EB1" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/21</t>
         </is>
       </c>
       <c r="EC1" t="inlineStr">
         <is>
-          <t>2026/07/21</t>
+          <t>2026/07/22</t>
         </is>
       </c>
       <c r="ED1" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="EE1" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/25</t>
         </is>
       </c>
     </row>
@@ -1243,10 +1243,10 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AK2" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="BU3" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="BY3" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -2261,10 +2261,10 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="BY4" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -2709,10 +2709,10 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="BY5" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H6" s="1" t="n">
@@ -3035,10 +3035,10 @@
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -3377,16 +3377,16 @@
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>V6-1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>00079754</t>
+          <t>00079996</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3401,39 +3401,39 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>30030-BG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1155</v>
+        <v>3200</v>
       </c>
       <c r="Q7" t="n">
-        <v>2310</v>
+        <v>6400</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>分割,スライス</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>東レペフ加工品株式会社</t>
+          <t>東レ株式会社</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>(国分・湖南用)</t>
+          <t>自動車材料事業部</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>00073871</t>
+          <t>00074110</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF7" s="1" t="n">
@@ -3483,10 +3483,10 @@
       </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>1155</v>
+        <v>3200</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -3506,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1155</v>
+        <v>3200</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3629,10 +3629,10 @@
         <v>0</v>
       </c>
       <c r="CF7" t="n">
-        <v>1155</v>
+        <v>0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="CH7" t="n">
         <v>0</v>
@@ -3821,20 +3821,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>V6-1</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>00079996</t>
+          <t>00079754</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3849,39 +3849,39 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-A   C</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3200</v>
+        <v>1155</v>
       </c>
       <c r="Q8" t="n">
-        <v>6400</v>
+        <v>2310</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>分割,スライス</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>東レ株式会社</t>
+          <t>東レペフ加工品株式会社</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>自動車材料事業部</t>
+          <t>(国分・湖南用)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>00074110</t>
+          <t>00073871</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF8" s="1" t="n">
@@ -3931,10 +3931,10 @@
       </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" s="1" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>3200</v>
+        <v>1155</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3200</v>
+        <v>1155</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -4077,13 +4077,13 @@
         <v>0</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="CG8" t="n">
         <v>0</v>
       </c>
       <c r="CH8" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H9" s="1" t="n">
@@ -4379,10 +4379,10 @@
       </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -4976,10 +4976,10 @@
         <v>0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="CH10" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="CI10" t="n">
         <v>0</v>
@@ -5413,13 +5413,13 @@
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="CE11" t="n">
         <v>4500</v>
       </c>
       <c r="CF11" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="CG11" t="n">
         <v>0</v>
@@ -5825,10 +5825,10 @@
         <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="BS12" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
         <v>0</v>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="AM13" t="n">
@@ -6189,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>6300</v>
+        <v>7200</v>
       </c>
       <c r="AQ13" t="n">
         <v>7200</v>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="BS13" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
         <v>0</v>
@@ -6288,10 +6288,10 @@
         <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="BX13" t="n">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
         <v>0</v>
@@ -6745,10 +6745,10 @@
         <v>0</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CA14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="n">
         <v>0</v>
@@ -7193,10 +7193,10 @@
         <v>0</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="CA15" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
@@ -7641,10 +7641,10 @@
         <v>0</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CA16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="n">
         <v>0</v>
@@ -8089,10 +8089,10 @@
         <v>0</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CA17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="n">
         <v>0</v>
@@ -8577,13 +8577,13 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CO18" t="n">
-        <v>2000</v>
+        <v>3400</v>
       </c>
       <c r="CP18" t="n">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="CQ18" t="n">
         <v>0</v>
@@ -9020,13 +9020,13 @@
         <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="CN19" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="CO19" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CP19" t="n">
         <v>0</v>
@@ -9469,13 +9469,13 @@
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="CO20" t="n">
-        <v>4000</v>
+        <v>6800</v>
       </c>
       <c r="CP20" t="n">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="CQ20" t="n">
         <v>0</v>
@@ -9912,13 +9912,13 @@
         <v>0</v>
       </c>
       <c r="CM21" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="CN21" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="CO21" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="CP21" t="n">
         <v>0</v>
@@ -10318,10 +10318,10 @@
         <v>0</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
         <v>0</v>
@@ -10772,10 +10772,10 @@
         <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1943</v>
       </c>
       <c r="CB23" t="n">
-        <v>1943</v>
+        <v>0</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -11208,10 +11208,10 @@
         <v>0</v>
       </c>
       <c r="BW24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BX24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BY24" t="n">
         <v>0</v>
@@ -11656,10 +11656,10 @@
         <v>0</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="BX25" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="BY25" t="n">
         <v>0</v>
@@ -12110,13 +12110,13 @@
         <v>0</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="BZ26" t="n">
-        <v>3900</v>
+        <v>2100</v>
       </c>
       <c r="CA26" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="CB26" t="n">
         <v>0</v>
@@ -12552,10 +12552,10 @@
         <v>0</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="BX27" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="BY27" t="n">
         <v>0</v>
@@ -13000,10 +13000,10 @@
         <v>0</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="BX28" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BY28" t="n">
         <v>0</v>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>020</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
@@ -13329,10 +13329,10 @@
       </c>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" s="1" t="n">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -13451,13 +13451,13 @@
         <v>0</v>
       </c>
       <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ29" t="n">
         <v>271</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>0</v>
       </c>
       <c r="CA29" t="n">
         <v>0</v>
@@ -13902,13 +13902,13 @@
         <v>0</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="BZ30" t="n">
-        <v>7800</v>
+        <v>4200</v>
       </c>
       <c r="CA30" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="CB30" t="n">
         <v>0</v>
@@ -14356,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="CA31" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CB31" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CC31" t="n">
         <v>0</v>
@@ -14813,10 +14813,10 @@
         <v>0</v>
       </c>
       <c r="CD32" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="CE32" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="CF32" t="n">
         <v>0</v>
@@ -15261,10 +15261,10 @@
         <v>0</v>
       </c>
       <c r="CD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CE33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CF33" t="n">
         <v>0</v>
@@ -15709,13 +15709,13 @@
         <v>0</v>
       </c>
       <c r="CD34" t="n">
-        <v>0</v>
+        <v>1940</v>
       </c>
       <c r="CE34" t="n">
         <v>1940</v>
       </c>
       <c r="CF34" t="n">
-        <v>1940</v>
+        <v>0</v>
       </c>
       <c r="CG34" t="n">
         <v>0</v>
@@ -16157,13 +16157,13 @@
         <v>0</v>
       </c>
       <c r="CD35" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CE35" t="n">
         <v>2000</v>
       </c>
       <c r="CF35" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CG35" t="n">
         <v>0</v>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>012</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
@@ -16611,7 +16611,7 @@
         <v>0</v>
       </c>
       <c r="CF36" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="CG36" t="n">
         <v>6000</v>
@@ -16620,19 +16620,19 @@
         <v>6000</v>
       </c>
       <c r="CI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK36" t="n">
         <v>6000</v>
-      </c>
-      <c r="CJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK36" t="n">
-        <v>0</v>
       </c>
       <c r="CL36" t="n">
         <v>6000</v>
       </c>
       <c r="CM36" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="CN36" t="n">
         <v>0</v>
@@ -17086,19 +17086,19 @@
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="CP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR37" t="n">
         <v>5000</v>
       </c>
-      <c r="CQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>0</v>
-      </c>
       <c r="CS37" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="CT37" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="BY38" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="BZ38" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="CA38" t="n">
         <v>0</v>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -17829,7 +17829,7 @@
         <v>4600</v>
       </c>
       <c r="AP39" t="n">
-        <v>7600</v>
+        <v>8800</v>
       </c>
       <c r="AQ39" t="n">
         <v>9000</v>
@@ -17928,13 +17928,13 @@
         <v>0</v>
       </c>
       <c r="BW39" t="n">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="BX39" t="n">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="BY39" t="n">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="BZ39" t="n">
         <v>0</v>
@@ -18382,10 +18382,10 @@
         <v>0</v>
       </c>
       <c r="BY40" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="CA40" t="n">
         <v>0</v>
@@ -18833,10 +18833,10 @@
         <v>0</v>
       </c>
       <c r="BZ41" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CA41" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CB41" t="n">
         <v>0</v>
@@ -19281,10 +19281,10 @@
         <v>0</v>
       </c>
       <c r="BZ42" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CA42" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CB42" t="n">
         <v>0</v>
@@ -19726,13 +19726,13 @@
         <v>0</v>
       </c>
       <c r="BY43" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="BZ43" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="CA43" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="CB43" t="n">
         <v>0</v>
@@ -20066,7 +20066,7 @@
         <v>0</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="AP44" t="n">
         <v>0</v>
@@ -20171,13 +20171,13 @@
         <v>0</v>
       </c>
       <c r="BX44" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="BY44" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="BZ44" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="CA44" t="n">
         <v>0</v>
@@ -20637,10 +20637,10 @@
         <v>0</v>
       </c>
       <c r="CD45" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CE45" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CF45" t="n">
         <v>0</v>
@@ -21085,10 +21085,10 @@
         <v>0</v>
       </c>
       <c r="CD46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CE46" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CF46" t="n">
         <v>0</v>
@@ -21533,10 +21533,10 @@
         <v>0</v>
       </c>
       <c r="CD47" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CE47" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CF47" t="n">
         <v>0</v>
@@ -21981,10 +21981,10 @@
         <v>0</v>
       </c>
       <c r="CD48" t="n">
-        <v>0</v>
+        <v>3995</v>
       </c>
       <c r="CE48" t="n">
-        <v>3995</v>
+        <v>0</v>
       </c>
       <c r="CF48" t="n">
         <v>0</v>
@@ -22453,10 +22453,10 @@
         <v>0</v>
       </c>
       <c r="CL49" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="CM49" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="CN49" t="n">
         <v>0</v>
@@ -22901,10 +22901,10 @@
         <v>0</v>
       </c>
       <c r="CL50" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CM50" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CN50" t="n">
         <v>0</v>
@@ -23349,10 +23349,10 @@
         <v>0</v>
       </c>
       <c r="CL51" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CM51" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
@@ -23797,10 +23797,10 @@
         <v>0</v>
       </c>
       <c r="CL52" t="n">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="CM52" t="n">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="CN52" t="n">
         <v>0</v>
@@ -24245,10 +24245,10 @@
         <v>0</v>
       </c>
       <c r="CL53" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="CM53" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
@@ -24693,10 +24693,10 @@
         <v>0</v>
       </c>
       <c r="CL54" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CM54" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="CN54" t="n">
         <v>0</v>
@@ -25127,10 +25127,10 @@
         <v>0</v>
       </c>
       <c r="CH55" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CI55" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CJ55" t="n">
         <v>0</v>
@@ -25570,10 +25570,10 @@
         <v>0</v>
       </c>
       <c r="CG56" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="CH56" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="CI56" t="n">
         <v>0</v>
@@ -26016,10 +26016,10 @@
         <v>0</v>
       </c>
       <c r="CG57" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CH57" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CI57" t="n">
         <v>0</v>
@@ -26465,10 +26465,10 @@
         <v>0</v>
       </c>
       <c r="CH58" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CI58" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CJ58" t="n">
         <v>0</v>
@@ -26908,10 +26908,10 @@
         <v>0</v>
       </c>
       <c r="CG59" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="CH59" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="CI59" t="n">
         <v>0</v>
@@ -27356,10 +27356,10 @@
         <v>0</v>
       </c>
       <c r="CG60" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CH60" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="CI60" t="n">
         <v>0</v>
@@ -27804,10 +27804,10 @@
         <v>0</v>
       </c>
       <c r="CG61" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CH61" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="CI61" t="n">
         <v>0</v>
@@ -28252,10 +28252,10 @@
         <v>0</v>
       </c>
       <c r="CG62" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CH62" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CI62" t="n">
         <v>0</v>
@@ -28700,10 +28700,10 @@
         <v>0</v>
       </c>
       <c r="CG63" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CH63" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CI63" t="n">
         <v>0</v>
@@ -29148,10 +29148,10 @@
         <v>0</v>
       </c>
       <c r="CG64" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CH64" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CI64" t="n">
         <v>0</v>
@@ -29585,16 +29585,16 @@
         <v>0</v>
       </c>
       <c r="CD65" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="CE65" t="n">
-        <v>2400</v>
+        <v>3300</v>
       </c>
       <c r="CF65" t="n">
         <v>3300</v>
       </c>
       <c r="CG65" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="CH65" t="n">
         <v>0</v>
@@ -29907,10 +29907,10 @@
         <v>2700</v>
       </c>
       <c r="AN66" t="n">
-        <v>2100</v>
+        <v>2700</v>
       </c>
       <c r="AO66" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AP66" t="n">
         <v>2100</v>
@@ -30000,10 +30000,10 @@
         <v>0</v>
       </c>
       <c r="BS66" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="BT66" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="BU66" t="n">
         <v>0</v>
@@ -30015,10 +30015,10 @@
         <v>0</v>
       </c>
       <c r="BX66" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="BY66" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="BZ66" t="n">
         <v>0</v>
@@ -30463,13 +30463,13 @@
         <v>0</v>
       </c>
       <c r="BX67" t="n">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="BY67" t="n">
-        <v>3300</v>
+        <v>3900</v>
       </c>
       <c r="BZ67" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="CA67" t="n">
         <v>0</v>
@@ -30938,10 +30938,10 @@
         <v>0</v>
       </c>
       <c r="CG68" t="n">
-        <v>0</v>
+        <v>2310</v>
       </c>
       <c r="CH68" t="n">
-        <v>2310</v>
+        <v>0</v>
       </c>
       <c r="CI68" t="n">
         <v>0</v>
@@ -31386,10 +31386,10 @@
         <v>0</v>
       </c>
       <c r="CG69" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="CH69" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="CI69" t="n">
         <v>0</v>
@@ -31846,10 +31846,10 @@
         <v>0</v>
       </c>
       <c r="CK70" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="CL70" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="CM70" t="n">
         <v>0</v>
@@ -32294,10 +32294,10 @@
         <v>0</v>
       </c>
       <c r="CK71" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CL71" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="CM71" t="n">
         <v>0</v>
@@ -32730,10 +32730,10 @@
         <v>0</v>
       </c>
       <c r="CG72" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="CH72" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="CI72" t="n">
         <v>0</v>

--- a/output/stage1_task_input_table.xlsx
+++ b/output/stage1_task_input_table.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EF85"/>
+  <dimension ref="A1:EF84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,457 +648,457 @@
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>2026/04/27</t>
+          <t>2026/04/28</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>2026/04/28</t>
+          <t>2026/04/29</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>2026/04/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/02</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>2026/05/02</t>
+          <t>2026/05/03</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>2026/05/03</t>
+          <t>2026/05/04</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>2026/05/04</t>
+          <t>2026/05/05</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>2026/05/05</t>
+          <t>2026/05/06</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>2026/05/06</t>
+          <t>2026/05/07</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>2026/05/09</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>2026/05/10</t>
+          <t>2026/05/11</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/05/12</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>2026/05/12</t>
+          <t>2026/05/13</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>2026/05/13</t>
+          <t>2026/05/14</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/05/16</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>2026/05/16</t>
+          <t>2026/05/17</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>2026/05/17</t>
+          <t>2026/05/18</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/21</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>2026/05/21</t>
+          <t>2026/05/22</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/23</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>2026/05/23</t>
+          <t>2026/05/24</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>2026/05/24</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/05/27</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>2026/05/27</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/05/31</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>2026/05/31</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/03</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>2026/06/03</t>
+          <t>2026/06/04</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>2026/06/04</t>
+          <t>2026/06/05</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>2026/06/05</t>
+          <t>2026/06/06</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>2026/06/06</t>
+          <t>2026/06/07</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>2026/06/07</t>
+          <t>2026/06/08</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>2026/06/08</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/06/10</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>2026/06/10</t>
+          <t>2026/06/11</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>2026/06/11</t>
+          <t>2026/06/12</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>2026/06/12</t>
+          <t>2026/06/13</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>2026/06/13</t>
+          <t>2026/06/14</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>2026/06/14</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/16</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/17</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>2026/06/17</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/06/20</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>2026/06/20</t>
+          <t>2026/06/21</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>2026/06/21</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/23</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>2026/06/23</t>
+          <t>2026/06/24</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/06/27</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>2026/06/30</t>
+          <t>2026/07/01</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/02</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/07/03</t>
         </is>
       </c>
       <c r="DI1" t="inlineStr">
         <is>
-          <t>2026/07/03</t>
+          <t>2026/07/04</t>
         </is>
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
-          <t>2026/07/04</t>
+          <t>2026/07/05</t>
         </is>
       </c>
       <c r="DK1" t="inlineStr">
         <is>
-          <t>2026/07/05</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="DL1" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="DM1" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="DN1" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/09</t>
         </is>
       </c>
       <c r="DO1" t="inlineStr">
         <is>
-          <t>2026/07/09</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="DP1" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/11</t>
         </is>
       </c>
       <c r="DQ1" t="inlineStr">
         <is>
-          <t>2026/07/11</t>
+          <t>2026/07/12</t>
         </is>
       </c>
       <c r="DR1" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="DS1" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="DT1" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/15</t>
         </is>
       </c>
       <c r="DU1" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="DV1" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="DW1" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="DX1" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/19</t>
         </is>
       </c>
       <c r="DY1" t="inlineStr">
         <is>
-          <t>2026/07/19</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="DZ1" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/21</t>
         </is>
       </c>
       <c r="EA1" t="inlineStr">
         <is>
-          <t>2026/07/21</t>
+          <t>2026/07/22</t>
         </is>
       </c>
       <c r="EB1" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="EC1" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="ED1" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="EE1" t="inlineStr">
         <is>
-          <t>2026/07/25</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/27</t>
         </is>
       </c>
     </row>
@@ -1385,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="CE2" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
@@ -1836,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="CF3" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="CE4" t="n">
-        <v>1155</v>
+        <v>0</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
@@ -2732,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="CF5" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
@@ -3177,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CE6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
@@ -3625,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CE7" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CF7" t="n">
         <v>0</v>
@@ -4076,10 +4076,10 @@
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CF8" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CG8" t="n">
         <v>0</v>
@@ -4524,10 +4524,10 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="CF9" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="CG9" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H10" s="1" t="n">
@@ -4829,10 +4829,10 @@
       </c>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
         <v>0</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CG11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
         <v>0</v>
@@ -5595,72 +5595,72 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>W5-13</t>
+          <t>V6-4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>00079641</t>
+          <t>00080129</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>15020-AX5R- 770X300F-A   P</t>
+          <t>15040-AA00-1000X 75F-ABK0C</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>15020-JX5R- 770X300F-A   R</t>
+          <t>15020-BA00-1000X 75F-ABK0C</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7200</v>
+        <v>150</v>
       </c>
       <c r="Q12" t="n">
-        <v>7200</v>
+        <v>300</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5675,17 +5675,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>00073775</t>
+          <t>00074208</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5702,53 +5702,53 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" s="1" t="n">
-        <v>46162</v>
+        <v>46178</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="AH12" s="1" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" s="1" t="n">
-        <v>46162</v>
+        <v>46181</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>7200</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7200</v>
+        <v>150</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -5826,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -5841,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         <v>0</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="CJ12" t="n">
         <v>0</v>
@@ -6043,72 +6043,72 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>W5-14</t>
+          <t>V6-5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>00079683</t>
+          <t>00080133</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10010-AP67-1550X 91F-A   P</t>
+          <t>15040-AA00-1000X150F-ABK0C</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>10010-JP67-1550X 20F-A   P</t>
+          <t>15020-BA00-1000X150F-ABK0C</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="Q13" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>00073817</t>
+          <t>00074209</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
@@ -6150,11 +6150,11 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" s="1" t="n">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -6163,20 +6163,20 @@
         </is>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -6184,19 +6184,19 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -6298,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="CJ13" t="n">
         <v>0</v>
@@ -6491,72 +6491,72 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C5-1</t>
+          <t>V6-6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>00079706</t>
+          <t>00080136</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20010-B600-1250X250F-AWH1C</t>
+          <t>30050-AV90-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20010-H600-1180X250F-AWH1C</t>
+          <t>30025-BV90-1000X200F-A   C</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="Q14" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>スリット,EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>00073845</t>
+          <t>00074210</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6598,11 +6598,11 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" s="1" t="n">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -6611,20 +6611,20 @@
         </is>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -6632,19 +6632,19 @@
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CJ14" t="n">
         <v>0</v>
@@ -6939,40 +6939,40 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>W5-16</t>
+          <t>V6-7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>00079686</t>
+          <t>00080137</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6987,24 +6987,24 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>10025-SR28-1650X180F-A   B</t>
+          <t>30050-AS60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>10025-JR28-1550X 20F-A   G</t>
+          <t>30025-BS60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="Q15" t="n">
-        <v>183</v>
+        <v>400</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>分割,スリット,EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>00073818</t>
+          <t>00074211</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
@@ -7046,11 +7046,11 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" s="1" t="n">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -7059,20 +7059,20 @@
         </is>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -7080,19 +7080,19 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -7194,7 +7194,7 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -7224,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CJ15" t="n">
         <v>0</v>
@@ -7387,72 +7387,72 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>W5-17</t>
+          <t>Y6-12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>00079687</t>
+          <t>00080128</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>15020-AW07-1550X271F-A   V</t>
+          <t>30040-AY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>15020-JW07-1550X 20F-A   V</t>
+          <t>30020-BY00- 640X250F-A   C</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>271</v>
+        <v>6000</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>12000</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>00073819</t>
+          <t>00074212</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
@@ -7494,33 +7494,33 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" s="1" t="n">
-        <v>46164</v>
+        <v>46177</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>46171</v>
+        <v>46188</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>46171</v>
+        <v>46188</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>46171</v>
+        <v>46188</v>
       </c>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" s="1" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
@@ -7528,19 +7528,19 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>20</v>
+        <v>6000</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20</v>
+        <v>6000</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -7642,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="CG16" t="n">
         <v>0</v>
@@ -7672,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="CI16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CJ16" t="n">
         <v>0</v>
@@ -7855,52 +7855,52 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>C5-1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>00080080</t>
+          <t>00079706</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>20010-B600-1250X250F-AWH1C</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>20010-H600-1180X250F-AWH1C</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="Q17" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>EC,欠点表示,巻返し</t>
+          <t>スリット,EC</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>00074188</t>
+          <t>00073845</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -7942,11 +7942,11 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" s="1" t="n">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -7955,20 +7955,20 @@
         </is>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" s="1" t="n">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
@@ -7976,19 +7976,19 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>1750</v>
+        <v>4000</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1750</v>
+        <v>4000</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -8090,7 +8090,7 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="CE17" t="n">
         <v>0</v>
@@ -8303,48 +8303,48 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>T6-3</t>
+          <t>W6-7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>00080061</t>
+          <t>00080110</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>30050-AG00-1030X200F-ABK0C</t>
+          <t>25025-JP17- 940X250F-A   Q</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>30050-JG00-1030X200F-ABK0Q</t>
+          <t>25025-JP17- 940X250F-A   Q</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="Q18" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>00074171</t>
+          <t>00074205</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -8390,7 +8390,7 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -8399,17 +8399,17 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF18" s="1" t="n">
-        <v>46181</v>
+        <v>46176</v>
       </c>
       <c r="AG18" s="1" t="n">
-        <v>46181</v>
+        <v>46176</v>
       </c>
       <c r="AH18" s="1" t="n">
-        <v>46181</v>
+        <v>46176</v>
       </c>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" s="1" t="n">
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -8550,10 +8550,10 @@
         <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="CD18" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CE18" t="n">
         <v>0</v>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H19" s="1" t="n">
@@ -8759,44 +8759,44 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>T6-4</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>00080063</t>
+          <t>00080080</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>30060-JG00-1000X100F-A   Q</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>200</v>
+        <v>1750</v>
       </c>
       <c r="Q19" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>00074172</t>
+          <t>00074188</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -8851,13 +8851,13 @@
         </is>
       </c>
       <c r="AF19" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AG19" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AH19" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" s="1" t="n">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>200</v>
+        <v>1750</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -8884,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>200</v>
+        <v>1750</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -8998,10 +8998,10 @@
         <v>0</v>
       </c>
       <c r="CC19" t="n">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="CD19" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CE19" t="n">
         <v>0</v>
@@ -9199,52 +9199,52 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>T6-5</t>
+          <t>E6-2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>00080064</t>
+          <t>00080100</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>30040-AG00-1050X200F-A   C</t>
+          <t>15020-AP17-1300X250F-A   P</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>30020-KG00-1050X200F-A   C</t>
+          <t>15020-NP17-1300X250F-A   J</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q20" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>EC,スライス</t>
+          <t>EC,巻返し</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>00074173</t>
+          <t>00074202</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -9286,7 +9286,7 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -9295,17 +9295,17 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AH20" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" s="1" t="n">
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -9446,10 +9446,10 @@
         <v>0</v>
       </c>
       <c r="CC20" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="CD20" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="CE20" t="n">
         <v>0</v>
@@ -9637,35 +9637,35 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>W6-3</t>
+          <t>E6-2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>00080065</t>
+          <t>00080100</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -9675,24 +9675,24 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>15020-AP17-1300X250F-A   P</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>15020-NP17-1300X250F-A   J</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>6000</v>
+        <v>250</v>
       </c>
       <c r="Q21" t="n">
-        <v>6000</v>
+        <v>250</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>EC,巻返し</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>00074175</t>
+          <t>00074203</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9734,7 +9734,7 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" s="1" t="n">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -9743,24 +9743,24 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>46189</v>
+        <v>46178</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>46189</v>
+        <v>46178</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>46189</v>
+        <v>46178</v>
       </c>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" s="1" t="n">
-        <v>46183</v>
+        <v>46175</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>46183</v>
+        <v>46175</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>6000</v>
+        <v>250</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -9780,7 +9780,7 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6000</v>
+        <v>250</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -9894,7 +9894,7 @@
         <v>0</v>
       </c>
       <c r="CC21" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="CD21" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="CL21" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="CM21" t="n">
         <v>0</v>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H22" s="1" t="n">
@@ -10103,44 +10103,44 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>W6-4</t>
+          <t>T6-3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>00080067</t>
+          <t>00080061</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30050-AG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30050-JG00-1030X200F-ABK0Q</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="Q22" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>スリット,EC,検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>00074176</t>
+          <t>00074171</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10182,7 +10182,7 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" s="1" t="n">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -10195,20 +10195,20 @@
         </is>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>46191</v>
+        <v>46181</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>46191</v>
+        <v>46181</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>46191</v>
+        <v>46181</v>
       </c>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" s="1" t="n">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>46185</v>
+        <v>46175</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -10228,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -10342,7 +10342,7 @@
         <v>0</v>
       </c>
       <c r="CC22" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CD22" t="n">
         <v>0</v>
@@ -10372,10 +10372,10 @@
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CN22" t="n">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="CO22" t="n">
         <v>0</v>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H23" s="1" t="n">
@@ -10551,44 +10551,44 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>W6-5</t>
+          <t>T6-4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>00080066</t>
+          <t>00080063</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30060-JG00-1000X100F-A   Q</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>9000</v>
+        <v>200</v>
       </c>
       <c r="Q23" t="n">
-        <v>9000</v>
+        <v>200</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>00074177</t>
+          <t>00074172</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -10630,7 +10630,7 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" s="1" t="n">
-        <v>46183</v>
+        <v>46174</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -10643,20 +10643,20 @@
         </is>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>46195</v>
+        <v>46181</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>46195</v>
+        <v>46181</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>46195</v>
+        <v>46181</v>
       </c>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" s="1" t="n">
-        <v>46183</v>
+        <v>46175</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>9000</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -10676,7 +10676,7 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9000</v>
+        <v>200</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -10790,7 +10790,7 @@
         <v>0</v>
       </c>
       <c r="CC23" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CD23" t="n">
         <v>0</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="CL23" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="CN23" t="n">
         <v>0</v>
@@ -10971,40 +10971,40 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>V5-9</t>
+          <t>T6-5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>00079688</t>
+          <t>00080064</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11019,24 +11019,24 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>30060-AG00-1030X200F-A   C</t>
+          <t>30040-AG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>30060-AG00-1030X100F-A   C</t>
+          <t>30020-KG00-1050X200F-A   C</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="Q24" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC,スライス</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>00073820</t>
+          <t>00074173</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11078,11 +11078,11 @@
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -11091,20 +11091,20 @@
         </is>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -11112,19 +11112,19 @@
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -11223,7 +11223,7 @@
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="BY24" t="n">
         <v>0</v>
@@ -11238,7 +11238,7 @@
         <v>0</v>
       </c>
       <c r="CC24" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="CD24" t="n">
         <v>0</v>
@@ -11419,87 +11419,87 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>W6-3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>00079913</t>
+          <t>00080065</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7A1 </t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0   </t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1980</v>
+        <v>6000</v>
       </c>
       <c r="Q25" t="n">
-        <v>1933</v>
+        <v>6000</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>東レペフ加工品株式会社</t>
+          <t>東レ株式会社</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>(国分・湖南用)</t>
+          <t>自動車材料事業部</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>00074031</t>
+          <t>00074175</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -11509,50 +11509,50 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" s="1" t="n">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>46171</v>
+        <v>46189</v>
       </c>
       <c r="AG25" s="1" t="n">
-        <v>46171</v>
+        <v>46189</v>
       </c>
       <c r="AH25" s="1" t="n">
-        <v>46171</v>
+        <v>46189</v>
       </c>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>1943</v>
+        <v>6000</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -11572,7 +11572,7 @@
         <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1943</v>
+        <v>6000</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -11677,7 +11677,7 @@
         <v>0</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1943</v>
+        <v>0</v>
       </c>
       <c r="CA25" t="n">
         <v>0</v>
@@ -11710,7 +11710,7 @@
         <v>0</v>
       </c>
       <c r="CK25" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="CL25" t="n">
         <v>0</v>
@@ -11867,40 +11867,40 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>W5-16</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>00079686</t>
+          <t>00080067</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11915,24 +11915,24 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10025-SR28-1650X180F-A   B</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>10025-JR28-1550X 20F-A   G</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>180</v>
+        <v>6000</v>
       </c>
       <c r="Q26" t="n">
-        <v>183</v>
+        <v>6000</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>分割,スリット,EC</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -11947,17 +11947,17 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>00073814</t>
+          <t>00074176</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11966,7 +11966,7 @@
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
@@ -11974,11 +11974,11 @@
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" s="1" t="n">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -11987,40 +11987,40 @@
         </is>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" s="1" t="n">
-        <v>46167</v>
+        <v>46184</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>46167</v>
+        <v>46185</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>20</v>
+        <v>6000</v>
       </c>
       <c r="AN26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>20</v>
+        <v>6000</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -12113,7 +12113,7 @@
         <v>0</v>
       </c>
       <c r="BV26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BW26" t="n">
         <v>0</v>
@@ -12161,10 +12161,10 @@
         <v>0</v>
       </c>
       <c r="CL26" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CM26" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="CN26" t="n">
         <v>0</v>
@@ -12315,72 +12315,72 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C5-1</t>
+          <t>W6-5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>00079706</t>
+          <t>00080066</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>20010-B600-1250X250F-AWH1C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>20010-H600-1180X250F-AWH1C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="Q27" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>スリット,EC</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -12395,17 +12395,17 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>00073846</t>
+          <t>00074177</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -12422,11 +12422,11 @@
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" s="1" t="n">
-        <v>46164</v>
+        <v>46183</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -12435,40 +12435,40 @@
         </is>
       </c>
       <c r="AF27" s="1" t="n">
-        <v>46171</v>
+        <v>46195</v>
       </c>
       <c r="AG27" s="1" t="n">
-        <v>46171</v>
+        <v>46195</v>
       </c>
       <c r="AH27" s="1" t="n">
-        <v>46171</v>
+        <v>46195</v>
       </c>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" s="1" t="n">
-        <v>46167</v>
+        <v>46183</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>46167</v>
+        <v>46184</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="AN27" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="AR27" t="n">
         <v>0</v>
@@ -12561,7 +12561,7 @@
         <v>0</v>
       </c>
       <c r="BV27" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="BW27" t="n">
         <v>0</v>
@@ -12606,10 +12606,10 @@
         <v>0</v>
       </c>
       <c r="CK27" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="CL27" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="CM27" t="n">
         <v>0</v>
@@ -12783,67 +12783,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46149</v>
+        <v>46164</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>00079398</t>
+          <t>00079913</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t xml:space="preserve">7A1 </t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t xml:space="preserve">0   </t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>6000</v>
+        <v>1980</v>
       </c>
       <c r="Q28" t="n">
-        <v>12000</v>
+        <v>1933</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>東レ株式会社</t>
+          <t>東レペフ加工品株式会社</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>自動車材料事業部</t>
+          <t>(国分・湖南用)</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>00073558</t>
+          <t>00074031</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -12858,28 +12858,28 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF28" s="1" t="n">
@@ -12893,10 +12893,10 @@
       </c>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
@@ -12904,19 +12904,19 @@
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>6000</v>
+        <v>1943</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6000</v>
+        <v>1943</v>
       </c>
       <c r="AR28" t="n">
         <v>0</v>
@@ -13015,10 +13015,10 @@
         <v>0</v>
       </c>
       <c r="BX28" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="BY28" t="n">
-        <v>2100</v>
+        <v>1943</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -13221,62 +13221,62 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>016</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>W5-14</t>
+          <t>C5-1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>00079683</t>
+          <t>00079706</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10010-AP67-1550X 91F-A   P</t>
+          <t>20010-B600-1250X250F-AWH1C</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10010-JP67-1550X 20F-A   P</t>
+          <t>20010-H600-1180X250F-AWH1C</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>91</v>
+        <v>2000</v>
       </c>
       <c r="Q29" t="n">
-        <v>90</v>
+        <v>2000</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>スリット,EC</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>00073812</t>
+          <t>00073846</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
@@ -13352,19 +13352,19 @@
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>91</v>
+        <v>2000</v>
       </c>
       <c r="AN29" t="n">
-        <v>91</v>
+        <v>2000</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>40</v>
+        <v>2000</v>
       </c>
       <c r="AQ29" t="n">
-        <v>91</v>
+        <v>2000</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="BV29" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="BW29" t="n">
         <v>0</v>
@@ -13669,30 +13669,30 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>017</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>W5-16</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>00079686</t>
+          <t>00079398</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13707,24 +13707,24 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10025-SR28-1650X180F-A   B</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>10025-JR28-1550X 20F-A   G</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>180</v>
+        <v>6000</v>
       </c>
       <c r="Q30" t="n">
-        <v>183</v>
+        <v>12000</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>分割,スリット,EC</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>00073813</t>
+          <t>00073558</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13758,7 +13758,7 @@
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
         <v>1</v>
@@ -13766,7 +13766,7 @@
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -13789,30 +13789,30 @@
       </c>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>180</v>
+        <v>6000</v>
       </c>
       <c r="AN30" t="n">
-        <v>180</v>
+        <v>6000</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>183</v>
+        <v>9600</v>
       </c>
       <c r="AQ30" t="n">
-        <v>180</v>
+        <v>6000</v>
       </c>
       <c r="AR30" t="n">
         <v>0</v>
@@ -13905,13 +13905,13 @@
         <v>0</v>
       </c>
       <c r="BV30" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="BY30" t="n">
         <v>0</v>
@@ -14117,62 +14117,62 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>016</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>W5-17</t>
+          <t>Y5-20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>00079687</t>
+          <t>00079398</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>15020-AW07-1550X271F-A   V</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>15020-JW07-1550X 20F-A   V</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>271</v>
+        <v>6000</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>12000</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>分割,EC</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -14187,17 +14187,17 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>00073815</t>
+          <t>00073557</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -14206,7 +14206,7 @@
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
@@ -14214,7 +14214,7 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF31" s="1" t="n">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" s="1" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="AK31" s="1" t="n">
         <v>46170</v>
@@ -14248,19 +14248,19 @@
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>271</v>
+        <v>12000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="AO31" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="AQ31" t="n">
-        <v>271</v>
+        <v>12000</v>
       </c>
       <c r="AR31" t="n">
         <v>0</v>
@@ -14356,13 +14356,13 @@
         <v>0</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="BY31" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="BZ31" t="n">
         <v>0</v>
@@ -14565,62 +14565,62 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0019</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46149</v>
+        <v>46170</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Y5-20</t>
+          <t>W5-22</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>00079398</t>
+          <t>00080126</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>13011-APR0-1500X 63F-A   X</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>13011-APR0-1500X 63F-A   X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>6000</v>
+        <v>63</v>
       </c>
       <c r="Q32" t="n">
-        <v>12000</v>
+        <v>63</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>00073557</t>
+          <t>00074207</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -14645,7 +14645,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0019</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -14662,7 +14662,7 @@
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" s="1" t="n">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF32" s="1" t="n">
@@ -14685,10 +14685,10 @@
       </c>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
@@ -14696,19 +14696,19 @@
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>12000</v>
+        <v>63</v>
       </c>
       <c r="AN32" t="n">
         <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12000</v>
+        <v>63</v>
       </c>
       <c r="AR32" t="n">
         <v>0</v>
@@ -14807,10 +14807,10 @@
         <v>0</v>
       </c>
       <c r="BX32" t="n">
-        <v>7800</v>
+        <v>0</v>
       </c>
       <c r="BY32" t="n">
-        <v>4200</v>
+        <v>63</v>
       </c>
       <c r="BZ32" t="n">
         <v>0</v>
@@ -15258,10 +15258,10 @@
         <v>0</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="BZ33" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CA33" t="n">
         <v>0</v>
@@ -15471,67 +15471,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>JR260601</t>
+          <t>W6-6</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>00079821</t>
+          <t>00080108</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7A1 </t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>FEL4004AY-10WD-1000X100</t>
+          <t>20020-AP17-1330X300F-A   P</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>40040-R10W- 316X 95</t>
+          <t>20020-AP17-1120X300F-A   P</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="Q34" t="n">
-        <v>2850</v>
+        <v>1500</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>東レペフ加工品株式会社</t>
+          <t>東レ株式会社</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>(国分・湖南用)</t>
+          <t>自動車材料事業部</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>00073962</t>
+          <t>00074204</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y34" t="n">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -15592,7 +15592,7 @@
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>950</v>
+        <v>1500</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -15604,7 +15604,7 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>950</v>
+        <v>1500</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -15715,10 +15715,10 @@
         <v>0</v>
       </c>
       <c r="CB34" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="CC34" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="CD34" t="n">
         <v>0</v>
@@ -15909,17 +15909,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>010</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>00073961</t>
+          <t>00073962</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -16040,7 +16040,7 @@
         </is>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -16052,7 +16052,7 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AR35" t="n">
         <v>0</v>
@@ -16163,10 +16163,10 @@
         <v>0</v>
       </c>
       <c r="CB35" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="CC35" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CD35" t="n">
         <v>0</v>
@@ -16357,30 +16357,30 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>JR260601</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>00079926</t>
+          <t>00079821</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -16390,25 +16390,25 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">0   </t>
+          <t>6780</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>FEL4004AY-10WD-1000X100</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>40040-R10W- 316X 95</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3995</v>
+        <v>1000</v>
       </c>
       <c r="Q36" t="n">
-        <v>3880</v>
+        <v>2850</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>00074045</t>
+          <t>00073961</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -16437,7 +16437,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -16449,7 +16449,7 @@
         <v>1</v>
       </c>
       <c r="Z36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
@@ -16467,20 +16467,20 @@
         </is>
       </c>
       <c r="AF36" s="1" t="n">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="AG36" s="1" t="n">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="AH36" s="1" t="n">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="AK36" s="1" t="n">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         </is>
       </c>
       <c r="AM36" t="n">
-        <v>3880</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3880</v>
+        <v>1000</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
@@ -16611,13 +16611,13 @@
         <v>0</v>
       </c>
       <c r="CB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CC36" t="n">
-        <v>1940</v>
+        <v>0</v>
       </c>
       <c r="CD36" t="n">
-        <v>1940</v>
+        <v>0</v>
       </c>
       <c r="CE36" t="n">
         <v>0</v>
@@ -16805,62 +16805,62 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>C6-1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>00080080</t>
+          <t>00080116</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>0R040-8Y0B- 820X200F-A   C</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>0R040-8Y0B- 310X200G-A   C</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1750</v>
+        <v>1600</v>
       </c>
       <c r="Q37" t="n">
-        <v>600</v>
+        <v>3200</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>EC,欠点表示,巻返し</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -16875,7 +16875,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>00074187</t>
+          <t>00074206</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -16902,16 +16902,16 @@
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF37" s="1" t="n">
@@ -16925,10 +16925,10 @@
       </c>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" s="1" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         </is>
       </c>
       <c r="AM37" t="n">
-        <v>1750</v>
+        <v>1600</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -16948,7 +16948,7 @@
         <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1750</v>
+        <v>1600</v>
       </c>
       <c r="AR37" t="n">
         <v>0</v>
@@ -17062,13 +17062,13 @@
         <v>0</v>
       </c>
       <c r="CC37" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CD37" t="n">
         <v>0</v>
       </c>
       <c r="CE37" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="CF37" t="n">
         <v>0</v>
@@ -17253,77 +17253,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>012</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>00080080</t>
+          <t>00079926</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t xml:space="preserve">7A1 </t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t xml:space="preserve">0   </t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>15025-AH1F-1550X250F-A   S</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>15025-JH1F-1550X250F-A   S</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1750</v>
+        <v>3995</v>
       </c>
       <c r="Q38" t="n">
-        <v>600</v>
+        <v>3880</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>EC,欠点表示,巻返し</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>東レ株式会社</t>
+          <t>東レペフ加工品株式会社</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>自動車材料事業部</t>
+          <t>(国分・湖南用)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>00074186</t>
+          <t>00074045</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -17333,19 +17333,19 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Y38" t="n">
         <v>1</v>
       </c>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
@@ -17354,12 +17354,12 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF38" s="1" t="n">
@@ -17373,10 +17373,10 @@
       </c>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         </is>
       </c>
       <c r="AM38" t="n">
-        <v>1750</v>
+        <v>3880</v>
       </c>
       <c r="AN38" t="n">
         <v>0</v>
@@ -17396,7 +17396,7 @@
         <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1750</v>
+        <v>3880</v>
       </c>
       <c r="AR38" t="n">
         <v>0</v>
@@ -17507,16 +17507,16 @@
         <v>0</v>
       </c>
       <c r="CB38" t="n">
-        <v>0</v>
+        <v>1940</v>
       </c>
       <c r="CC38" t="n">
-        <v>0</v>
+        <v>1940</v>
       </c>
       <c r="CD38" t="n">
         <v>0</v>
       </c>
       <c r="CE38" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="CF38" t="n">
         <v>0</v>
@@ -17701,77 +17701,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>JR260602</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>00079926</t>
+          <t>00080080</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7A1 </t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0   </t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>FEL3002BY05-10WD-1000X 95   LG</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   LG</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3995</v>
+        <v>1750</v>
       </c>
       <c r="Q39" t="n">
-        <v>3880</v>
+        <v>600</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>東レペフ加工品株式会社</t>
+          <t>東レ株式会社</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>(国分・湖南用)</t>
+          <t>自動車材料事業部</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>00074044</t>
+          <t>00074187</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -17781,19 +17781,19 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y39" t="n">
         <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
@@ -17802,12 +17802,12 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF39" s="1" t="n">
@@ -17821,10 +17821,10 @@
       </c>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="AM39" t="n">
-        <v>4000</v>
+        <v>1750</v>
       </c>
       <c r="AN39" t="n">
         <v>0</v>
@@ -17844,7 +17844,7 @@
         <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>4000</v>
+        <v>1750</v>
       </c>
       <c r="AR39" t="n">
         <v>0</v>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="CC39" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CD39" t="n">
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="CE39" t="n">
         <v>0</v>
@@ -18149,62 +18149,62 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>巻返し</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>T6-1</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>00079994</t>
+          <t>00080080</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>30100-NG00-1000X100F-A   C</t>
+          <t>15025-AH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>30100-VG00-1000X100F-A   C</t>
+          <t>15025-JH1F-1550X250F-A   S</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="Q40" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>エンボス,巻返し</t>
+          <t>EC,欠点表示,巻返し</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>00074136</t>
+          <t>00074186</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -18246,11 +18246,11 @@
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" s="1" t="n">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
@@ -18259,20 +18259,20 @@
         </is>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" s="1" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="AM40" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -18292,7 +18292,7 @@
         <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="AR40" t="n">
         <v>0</v>
@@ -18409,13 +18409,13 @@
         <v>0</v>
       </c>
       <c r="CD40" t="n">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="CE40" t="n">
         <v>0</v>
       </c>
       <c r="CF40" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="CG40" t="n">
         <v>0</v>
@@ -18597,77 +18597,77 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>W6-1</t>
+          <t>JR260602</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>00080081</t>
+          <t>00079926</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t xml:space="preserve">7A1 </t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t xml:space="preserve">0   </t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>20020-AP17-1440X300F-A   P</t>
+          <t>FEL3002BY05-10WD-1000X 95   LG</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>20020-AP17-1410X300F-A   V</t>
+          <t>30020-A05W- 870X 97   LG</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>600</v>
+        <v>3995</v>
       </c>
       <c r="Q41" t="n">
-        <v>600</v>
+        <v>3880</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>東レ株式会社</t>
+          <t>東レペフ加工品株式会社</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>自動車材料事業部</t>
+          <t>(国分・湖南用)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>00074189</t>
+          <t>00074044</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -18677,28 +18677,28 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Y41" t="n">
         <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" s="1" t="n">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -18707,17 +18707,17 @@
         </is>
       </c>
       <c r="AF41" s="1" t="n">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="AG41" s="1" t="n">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="AH41" s="1" t="n">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" s="1" t="n">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="AK41" s="1" t="n">
         <v>46175</v>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="AM41" t="n">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -18740,7 +18740,7 @@
         <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
@@ -18851,13 +18851,13 @@
         <v>0</v>
       </c>
       <c r="CB41" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CC41" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CD41" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="CE41" t="n">
         <v>0</v>
@@ -19045,62 +19045,62 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>巻返し</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>T6-1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>00079927</t>
+          <t>00079994</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>20025-AX17-1050X300F-A   E</t>
+          <t>30100-NG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>20025-AX17-1000X300F-A   E</t>
+          <t>30100-VG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>29400</v>
+        <v>500</v>
       </c>
       <c r="Q42" t="n">
-        <v>29400</v>
+        <v>500</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>エンボス,巻返し</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -19115,7 +19115,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>00074046</t>
+          <t>00074136</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -19125,7 +19125,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -19137,38 +19137,38 @@
         <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t xml:space="preserve">O </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF42" s="1" t="n">
-        <v>46185</v>
+        <v>46181</v>
       </c>
       <c r="AG42" s="1" t="n">
-        <v>46185</v>
+        <v>46181</v>
       </c>
       <c r="AH42" s="1" t="n">
-        <v>46185</v>
+        <v>46181</v>
       </c>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AK42" s="1" t="n">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         </is>
       </c>
       <c r="AM42" t="n">
-        <v>29400</v>
+        <v>500</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -19188,7 +19188,7 @@
         <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>29400</v>
+        <v>500</v>
       </c>
       <c r="AR42" t="n">
         <v>0</v>
@@ -19308,13 +19308,13 @@
         <v>0</v>
       </c>
       <c r="CE42" t="n">
-        <v>5400</v>
+        <v>500</v>
       </c>
       <c r="CF42" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="CG42" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="CH42" t="n">
         <v>0</v>
@@ -19323,10 +19323,10 @@
         <v>0</v>
       </c>
       <c r="CJ42" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="CK42" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="CL42" t="n">
         <v>0</v>
@@ -19503,20 +19503,20 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>W6-1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>00079987</t>
+          <t>00080081</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -19531,24 +19531,24 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>20020-AP17-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>20020-AP17-1410X300F-A   V</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="Q43" t="n">
-        <v>12000</v>
+        <v>600</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>00074120</t>
+          <t>00074189</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -19590,33 +19590,33 @@
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K </t>
+        </is>
+      </c>
+      <c r="AF43" s="1" t="n">
         <v>46182</v>
       </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>スリット機1　湖南</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="AF43" s="1" t="n">
-        <v>46188</v>
-      </c>
       <c r="AG43" s="1" t="n">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" s="1" t="n">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="AM43" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="AN43" t="n">
         <v>0</v>
@@ -19636,7 +19636,7 @@
         <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="AR43" t="n">
         <v>0</v>
@@ -19750,7 +19750,7 @@
         <v>0</v>
       </c>
       <c r="CC43" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="CD43" t="n">
         <v>0</v>
@@ -19780,7 +19780,7 @@
         <v>0</v>
       </c>
       <c r="CM43" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="CN43" t="n">
         <v>0</v>
@@ -19941,30 +19941,30 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>欠点表示</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>021</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Y6-9</t>
+          <t>E6-1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>00079987</t>
+          <t>00079927</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -19979,24 +19979,24 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>30030-AP66-1110X300F-ABK0M</t>
+          <t>20025-AX17-1050X300F-A   E</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>30030-AP66- 550X300F-ABK0M</t>
+          <t>20025-AX17-1000X300F-A   E</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>6000</v>
+        <v>29400</v>
       </c>
       <c r="Q44" t="n">
-        <v>12000</v>
+        <v>29400</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>欠点表示,スリット</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>00074119</t>
+          <t>00074046</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -20021,7 +20021,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -20033,12 +20033,12 @@
         <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" s="1" t="n">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
@@ -20047,24 +20047,24 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">O </t>
         </is>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" s="1" t="n">
-        <v>46184</v>
+        <v>46176</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         </is>
       </c>
       <c r="AM44" t="n">
-        <v>12000</v>
+        <v>29400</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
@@ -20084,7 +20084,7 @@
         <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>12000</v>
+        <v>29400</v>
       </c>
       <c r="AR44" t="n">
         <v>0</v>
@@ -20201,13 +20201,13 @@
         <v>0</v>
       </c>
       <c r="CD44" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="CE44" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="CF44" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="CG44" t="n">
         <v>0</v>
@@ -20219,16 +20219,16 @@
         <v>0</v>
       </c>
       <c r="CJ44" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="CK44" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="CL44" t="n">
         <v>0</v>
       </c>
       <c r="CM44" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="CN44" t="n">
         <v>0</v>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>023</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
@@ -20407,12 +20407,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Y6-10</t>
+          <t>Y6-9</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>00079985</t>
+          <t>00079987</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -20437,10 +20437,10 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="Q45" t="n">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>00074118</t>
+          <t>00074120</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -20486,7 +20486,7 @@
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
@@ -20499,20 +20499,20 @@
         </is>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" s="1" t="n">
-        <v>46185</v>
+        <v>46181</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>46185</v>
+        <v>46181</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="AM45" t="n">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -20532,7 +20532,7 @@
         <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="AR45" t="n">
         <v>0</v>
@@ -20664,7 +20664,7 @@
         <v>0</v>
       </c>
       <c r="CI45" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="CJ45" t="n">
         <v>0</v>
@@ -20679,7 +20679,7 @@
         <v>0</v>
       </c>
       <c r="CN45" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="CO45" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>022</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
@@ -20855,12 +20855,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Y6-10</t>
+          <t>Y6-9</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>00079985</t>
+          <t>00079987</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -20885,10 +20885,10 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="Q46" t="n">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>00074117</t>
+          <t>00074119</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -20934,7 +20934,7 @@
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
@@ -20947,20 +20947,20 @@
         </is>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" s="1" t="n">
-        <v>46185</v>
+        <v>46181</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>46185</v>
+        <v>46181</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         </is>
       </c>
       <c r="AM46" t="n">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -20980,7 +20980,7 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="AR46" t="n">
         <v>0</v>
@@ -21112,7 +21112,7 @@
         <v>0</v>
       </c>
       <c r="CI46" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="CJ46" t="n">
         <v>0</v>
@@ -21127,7 +21127,7 @@
         <v>0</v>
       </c>
       <c r="CN46" t="n">
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="CO46" t="n">
         <v>0</v>
@@ -21285,17 +21285,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>011</t>
         </is>
       </c>
       <c r="H47" s="1" t="n">
@@ -21303,44 +21303,44 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>V6-2</t>
+          <t>Y6-10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>00079995</t>
+          <t>00079985</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X200F-A   C</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>30060-AG00-1000X100F-A   C</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>10000</v>
+        <v>5400</v>
       </c>
       <c r="Q47" t="n">
-        <v>10000</v>
+        <v>10800</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -21355,7 +21355,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>00074112</t>
+          <t>00074118</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -21382,7 +21382,7 @@
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" s="1" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
@@ -21395,20 +21395,20 @@
         </is>
       </c>
       <c r="AF47" s="1" t="n">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="AG47" s="1" t="n">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="AH47" s="1" t="n">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="AK47" s="1" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         </is>
       </c>
       <c r="AM47" t="n">
-        <v>10000</v>
+        <v>5400</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
@@ -21428,7 +21428,7 @@
         <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>10000</v>
+        <v>5400</v>
       </c>
       <c r="AR47" t="n">
         <v>0</v>
@@ -21572,10 +21572,10 @@
         <v>0</v>
       </c>
       <c r="CM47" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="CN47" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="CO47" t="n">
         <v>0</v>
@@ -21584,7 +21584,7 @@
         <v>0</v>
       </c>
       <c r="CQ47" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="CR47" t="n">
         <v>0</v>
@@ -21733,30 +21733,30 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>欠点表示</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>W6-4</t>
+          <t>Y6-10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>00080067</t>
+          <t>00079985</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -21771,24 +21771,24 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
+          <t>30030-AP66-1110X300F-ABK0M</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30030-AP66- 550X300F-ABK0M</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>6000</v>
+        <v>5400</v>
       </c>
       <c r="Q48" t="n">
-        <v>6000</v>
+        <v>10800</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>スリット,EC,検査</t>
+          <t>欠点表示,スリット</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>00074178</t>
+          <t>00074117</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -21830,11 +21830,11 @@
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
@@ -21843,20 +21843,20 @@
         </is>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         </is>
       </c>
       <c r="AM48" t="n">
-        <v>6000</v>
+        <v>10800</v>
       </c>
       <c r="AN48" t="n">
         <v>0</v>
@@ -21876,7 +21876,7 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>6000</v>
+        <v>10800</v>
       </c>
       <c r="AR48" t="n">
         <v>0</v>
@@ -22017,10 +22017,10 @@
         <v>0</v>
       </c>
       <c r="CL48" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="CM48" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="CN48" t="n">
         <v>0</v>
@@ -22171,40 +22171,40 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Y5-34</t>
+          <t>V6-2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>00079583</t>
+          <t>00079995</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -22219,24 +22219,24 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-A   C</t>
+          <t>30060-AG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-A   C</t>
+          <t>30060-AG00-1000X100F-A   C</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="Q49" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>00073728</t>
+          <t>00074112</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -22278,33 +22278,33 @@
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" s="1" t="n">
-        <v>46168</v>
+        <v>46184</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>46170</v>
+        <v>46190</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>46170</v>
+        <v>46190</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>46170</v>
+        <v>46190</v>
       </c>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" s="1" t="n">
-        <v>46169</v>
+        <v>46185</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>46169</v>
+        <v>46188</v>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         </is>
       </c>
       <c r="AM49" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
@@ -22324,7 +22324,7 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="AR49" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
         <v>0</v>
       </c>
       <c r="BX49" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="BY49" t="n">
         <v>0</v>
@@ -22468,7 +22468,7 @@
         <v>0</v>
       </c>
       <c r="CM49" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="CN49" t="n">
         <v>0</v>
@@ -22477,7 +22477,7 @@
         <v>0</v>
       </c>
       <c r="CP49" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="CQ49" t="n">
         <v>0</v>
@@ -22619,72 +22619,72 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Y5-35</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>00079676</t>
+          <t>00080067</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>30040-AG00- 935X200F-AGA1C</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>30020-KG00- 935X200F-AGA1C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1600</v>
+        <v>6000</v>
       </c>
       <c r="Q50" t="n">
-        <v>3200</v>
+        <v>6000</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>00073803</t>
+          <t>00074178</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -22726,11 +22726,11 @@
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" s="1" t="n">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
@@ -22739,20 +22739,20 @@
         </is>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" s="1" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         </is>
       </c>
       <c r="AM50" t="n">
-        <v>1600</v>
+        <v>6000</v>
       </c>
       <c r="AN50" t="n">
         <v>0</v>
@@ -22772,7 +22772,7 @@
         <v>0</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1600</v>
+        <v>6000</v>
       </c>
       <c r="AR50" t="n">
         <v>0</v>
@@ -22874,7 +22874,7 @@
         <v>0</v>
       </c>
       <c r="BY50" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="BZ50" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="CK50" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="CL50" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="CM50" t="n">
         <v>0</v>
@@ -23091,68 +23091,68 @@
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>JR260503</t>
+          <t>Y5-35</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>00079913</t>
+          <t>00079676</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7A1 </t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0   </t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>FEL3002BGB-05WD-1000X100   BKB</t>
+          <t>30040-AG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>30020-A05W- 870X 97   BKB</t>
+          <t>30020-KG00- 935X200F-AGA1C</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1980</v>
+        <v>1600</v>
       </c>
       <c r="Q51" t="n">
-        <v>1933</v>
+        <v>3200</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>SEC,梱包,スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>東レペフ加工品株式会社</t>
+          <t>東レ株式会社</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>(国分・湖南用)</t>
+          <t>自動車材料事業部</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>00074033</t>
+          <t>00073803</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0:未完</t>
+          <t>1:完了</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -23162,19 +23162,19 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" s="1" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF51" s="1" t="n">
@@ -23208,19 +23208,19 @@
         </is>
       </c>
       <c r="AM51" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="AQ51" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="AR51" t="n">
         <v>0</v>
@@ -23319,10 +23319,10 @@
         <v>0</v>
       </c>
       <c r="BX51" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="BY51" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="BZ51" t="n">
         <v>0</v>
@@ -23535,67 +23535,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Y5-38</t>
+          <t>JR260503</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>00079823</t>
+          <t>00079913</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t xml:space="preserve">7A1 </t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t xml:space="preserve">0   </t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>50080-AY0B- 850X200F-AGA1C</t>
+          <t>FEL3002BGB-05WD-1000X100   BKB</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 850X200F-AGA1C</t>
+          <t>30020-A05W- 870X 97   BKB</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2000</v>
+        <v>1980</v>
       </c>
       <c r="Q52" t="n">
-        <v>4000</v>
+        <v>1933</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>SEC,梱包,スリット</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>東レ株式会社</t>
+          <t>東レペフ加工品株式会社</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>自動車材料事業部</t>
+          <t>(国分・湖南用)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>00073958</t>
+          <t>00074033</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -23610,14 +23610,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
@@ -23659,13 +23659,13 @@
         <v>2000</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>776</v>
       </c>
       <c r="AQ52" t="n">
         <v>2000</v>
@@ -23767,10 +23767,10 @@
         <v>0</v>
       </c>
       <c r="BX52" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="BY52" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="BZ52" t="n">
         <v>0</v>
@@ -23983,20 +23983,20 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46149</v>
+        <v>46162</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Y5-26</t>
+          <t>Y5-38</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>00079404</t>
+          <t>00079823</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -24011,20 +24011,20 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1C</t>
+          <t>50080-AY0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>0R040-8Y0B- 850X200F-AGA1C</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="Q53" t="n">
-        <v>14000</v>
+        <v>4000</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>00073564</t>
+          <t>00073958</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -24070,7 +24070,7 @@
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF53" s="1" t="n">
@@ -24093,7 +24093,7 @@
       </c>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="AK53" s="1" t="n">
         <v>46170</v>
@@ -24104,19 +24104,19 @@
         </is>
       </c>
       <c r="AM53" t="n">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="AN53" t="n">
         <v>0</v>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AP53" t="n">
         <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="AR53" t="n">
         <v>0</v>
@@ -24215,10 +24215,10 @@
         <v>0</v>
       </c>
       <c r="BX53" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="BY53" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BZ53" t="n">
         <v>0</v>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>017</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
@@ -24439,12 +24439,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Y5-28</t>
+          <t>Y5-26</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>00079408</t>
+          <t>00079404</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -24459,20 +24459,20 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1C</t>
+          <t>50080-AY0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="Q54" t="n">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>00073566</t>
+          <t>00073564</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -24518,7 +24518,7 @@
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
@@ -24541,10 +24541,10 @@
       </c>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="AK54" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
@@ -24552,19 +24552,19 @@
         </is>
       </c>
       <c r="AM54" t="n">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="AN54" t="n">
-        <v>4600</v>
+        <v>3600</v>
       </c>
       <c r="AO54" t="n">
-        <v>4400</v>
+        <v>3400</v>
       </c>
       <c r="AP54" t="n">
-        <v>9200</v>
+        <v>6000</v>
       </c>
       <c r="AQ54" t="n">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="AR54" t="n">
         <v>0</v>
@@ -24660,10 +24660,10 @@
         <v>0</v>
       </c>
       <c r="BW54" t="n">
-        <v>4600</v>
+        <v>3000</v>
       </c>
       <c r="BX54" t="n">
-        <v>4400</v>
+        <v>4000</v>
       </c>
       <c r="BY54" t="n">
         <v>0</v>
@@ -25123,10 +25123,10 @@
         <v>0</v>
       </c>
       <c r="CB55" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CC55" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CD55" t="n">
         <v>0</v>
@@ -25571,10 +25571,10 @@
         <v>0</v>
       </c>
       <c r="CB56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="CC56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="CD56" t="n">
         <v>0</v>
@@ -26019,10 +26019,10 @@
         <v>0</v>
       </c>
       <c r="CB57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CC57" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CD57" t="n">
         <v>0</v>
@@ -26467,10 +26467,10 @@
         <v>0</v>
       </c>
       <c r="CB58" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="CC58" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="CD58" t="n">
         <v>0</v>
@@ -26915,10 +26915,10 @@
         <v>0</v>
       </c>
       <c r="CB59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="CC59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="CD59" t="n">
         <v>0</v>
@@ -27363,10 +27363,10 @@
         <v>0</v>
       </c>
       <c r="CB60" t="n">
-        <v>0</v>
+        <v>3995</v>
       </c>
       <c r="CC60" t="n">
-        <v>3995</v>
+        <v>0</v>
       </c>
       <c r="CD60" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="CJ61" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="CK61" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="CL61" t="n">
         <v>0</v>
@@ -28283,10 +28283,10 @@
         <v>0</v>
       </c>
       <c r="CJ62" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CK62" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CL62" t="n">
         <v>0</v>
@@ -28731,10 +28731,10 @@
         <v>0</v>
       </c>
       <c r="CJ63" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CK63" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="CL63" t="n">
         <v>0</v>
@@ -29179,10 +29179,10 @@
         <v>0</v>
       </c>
       <c r="CJ64" t="n">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="CK64" t="n">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="CL64" t="n">
         <v>0</v>
@@ -29627,10 +29627,10 @@
         <v>0</v>
       </c>
       <c r="CJ65" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="CK65" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="CL65" t="n">
         <v>0</v>
@@ -30075,10 +30075,10 @@
         <v>0</v>
       </c>
       <c r="CJ66" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CK66" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="CL66" t="n">
         <v>0</v>
@@ -30499,10 +30499,10 @@
         <v>0</v>
       </c>
       <c r="CB67" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CC67" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="CD67" t="n">
         <v>0</v>
@@ -30947,10 +30947,10 @@
         <v>0</v>
       </c>
       <c r="CB68" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CC68" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CD68" t="n">
         <v>0</v>
@@ -31404,10 +31404,10 @@
         <v>0</v>
       </c>
       <c r="CE69" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CF69" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="CG69" t="n">
         <v>0</v>
@@ -31852,10 +31852,10 @@
         <v>0</v>
       </c>
       <c r="CE70" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CF70" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CG70" t="n">
         <v>0</v>
@@ -32300,10 +32300,10 @@
         <v>0</v>
       </c>
       <c r="CE71" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="CF71" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="CG71" t="n">
         <v>0</v>
@@ -32748,10 +32748,10 @@
         <v>0</v>
       </c>
       <c r="CE72" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="CF72" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="CG72" t="n">
         <v>0</v>
@@ -33187,10 +33187,10 @@
         <v>0</v>
       </c>
       <c r="CB73" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CC73" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CD73" t="n">
         <v>0</v>
@@ -33635,10 +33635,10 @@
         <v>0</v>
       </c>
       <c r="CB74" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CC74" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CD74" t="n">
         <v>0</v>
@@ -34083,10 +34083,10 @@
         <v>0</v>
       </c>
       <c r="CB75" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CC75" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CD75" t="n">
         <v>0</v>
@@ -34531,10 +34531,10 @@
         <v>0</v>
       </c>
       <c r="CB76" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CC76" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CD76" t="n">
         <v>0</v>
@@ -34725,92 +34725,92 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>0012</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>W5-13</t>
+          <t>A6-1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>00079641</t>
+          <t>00079754</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>15020-AX5R- 770X300F-A   P</t>
+          <t>40100-AG00-1080X105F-A</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>15020-JX5R- 770X300F-A   R</t>
+          <t>40050-BG00-1080X210F-A   X</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>7200</v>
+        <v>1155</v>
       </c>
       <c r="Q77" t="n">
-        <v>7200</v>
+        <v>2310</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スライス,接続</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>東レ株式会社</t>
+          <t>東レペフ加工品株式会社</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>自動車材料事業部</t>
+          <t>(国分・湖南用)</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>00073776</t>
+          <t>00073872</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>1:完了</t>
+          <t>0:未完</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>0012</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Y77" t="n">
@@ -34822,11 +34822,11 @@
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" s="1" t="n">
-        <v>46162</v>
+        <v>46175</v>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
@@ -34835,20 +34835,20 @@
         </is>
       </c>
       <c r="AF77" s="1" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="AG77" s="1" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="AH77" s="1" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="AI77" t="inlineStr"/>
       <c r="AJ77" s="1" t="n">
-        <v>46168</v>
+        <v>46177</v>
       </c>
       <c r="AK77" s="1" t="n">
-        <v>46169</v>
+        <v>46177</v>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
@@ -34856,19 +34856,19 @@
         </is>
       </c>
       <c r="AM77" t="n">
-        <v>7200</v>
+        <v>2310</v>
       </c>
       <c r="AN77" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="AO77" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="AP77" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="AQ77" t="n">
-        <v>7200</v>
+        <v>2310</v>
       </c>
       <c r="AR77" t="n">
         <v>0</v>
@@ -34964,10 +34964,10 @@
         <v>0</v>
       </c>
       <c r="BW77" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="BX77" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="BY77" t="n">
         <v>0</v>
@@ -34988,7 +34988,7 @@
         <v>0</v>
       </c>
       <c r="CE77" t="n">
-        <v>0</v>
+        <v>2310</v>
       </c>
       <c r="CF77" t="n">
         <v>0</v>
@@ -35183,67 +35183,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>A6-1</t>
+          <t>V5-8</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>00079754</t>
+          <t>00079605</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>40100-AG00-1080X105F-A</t>
+          <t>30030-AT60-1000X200F-A   F</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
-          <t>40050-BG00-1080X210F-A   X</t>
+          <t>30030-AT60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1155</v>
+        <v>1400</v>
       </c>
       <c r="Q78" t="n">
-        <v>2310</v>
+        <v>1400</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>スライス,接続</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>東レペフ加工品株式会社</t>
+          <t>東レ株式会社</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>(国分・湖南用)</t>
+          <t>自動車材料事業部</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>00073872</t>
+          <t>00073737</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y78" t="n">
@@ -35270,26 +35270,26 @@
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF78" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="AG78" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="AH78" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="AI78" t="inlineStr"/>
       <c r="AJ78" s="1" t="n">
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="AM78" t="n">
-        <v>2310</v>
+        <v>1400</v>
       </c>
       <c r="AN78" t="n">
         <v>0</v>
@@ -35316,7 +35316,7 @@
         <v>0</v>
       </c>
       <c r="AQ78" t="n">
-        <v>2310</v>
+        <v>1400</v>
       </c>
       <c r="AR78" t="n">
         <v>0</v>
@@ -35436,10 +35436,10 @@
         <v>0</v>
       </c>
       <c r="CE78" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="CF78" t="n">
-        <v>2310</v>
+        <v>0</v>
       </c>
       <c r="CG78" t="n">
         <v>0</v>
@@ -35631,52 +35631,52 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>V5-8</t>
+          <t>Y6-3</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>00079605</t>
+          <t>00079871</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   F</t>
+          <t>50080-AY0B- 870X200F-ABG1F</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1400</v>
+        <v>3200</v>
       </c>
       <c r="Q79" t="n">
-        <v>1400</v>
+        <v>6400</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>接続,SEC</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -35691,7 +35691,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>00073737</t>
+          <t>00073993</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -35718,7 +35718,7 @@
       <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
@@ -35727,24 +35727,24 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t xml:space="preserve">S </t>
+          <t xml:space="preserve">K </t>
         </is>
       </c>
       <c r="AF79" s="1" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="AG79" s="1" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="AH79" s="1" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="AI79" t="inlineStr"/>
       <c r="AJ79" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="AK79" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         </is>
       </c>
       <c r="AM79" t="n">
-        <v>1400</v>
+        <v>3200</v>
       </c>
       <c r="AN79" t="n">
         <v>0</v>
@@ -35764,7 +35764,7 @@
         <v>0</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1400</v>
+        <v>3200</v>
       </c>
       <c r="AR79" t="n">
         <v>0</v>
@@ -35887,7 +35887,7 @@
         <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>1400</v>
+        <v>3200</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H80" s="1" t="n">
@@ -36087,12 +36087,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Y6-3</t>
+          <t>Y6-4</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>00079871</t>
+          <t>00079872</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -36107,21 +36107,21 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-ABG1F</t>
+          <t>50080-AY0B- 870X200F-AGA1F</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 870X200F-AGA1H</t>
         </is>
       </c>
       <c r="P80" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q80" t="n">
         <v>3200</v>
       </c>
-      <c r="Q80" t="n">
-        <v>6400</v>
-      </c>
       <c r="R80" t="inlineStr">
         <is>
           <t>接続,SEC</t>
@@ -36139,7 +36139,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>00073993</t>
+          <t>00073994</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -36158,7 +36158,7 @@
         </is>
       </c>
       <c r="Y80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z80" t="n">
         <v>1</v>
@@ -36170,7 +36170,7 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr">
@@ -36200,7 +36200,7 @@
         </is>
       </c>
       <c r="AM80" t="n">
-        <v>3200</v>
+        <v>1600</v>
       </c>
       <c r="AN80" t="n">
         <v>0</v>
@@ -36212,7 +36212,7 @@
         <v>0</v>
       </c>
       <c r="AQ80" t="n">
-        <v>3200</v>
+        <v>1600</v>
       </c>
       <c r="AR80" t="n">
         <v>0</v>
@@ -36335,10 +36335,10 @@
         <v>0</v>
       </c>
       <c r="CF80" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CG80" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="CH80" t="n">
         <v>0</v>
@@ -36527,7 +36527,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H81" s="1" t="n">
@@ -36535,12 +36535,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Y6-4</t>
+          <t>Y6-5</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>00079872</t>
+          <t>00079873</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -36555,20 +36555,20 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>50080-AY0B- 870X200F-AGA1F</t>
+          <t>50080-AY0B- 680X200F-ABG1F</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-AGA1H</t>
+          <t>0R040-8Y0B- 680X200F-ABG1C</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="Q81" t="n">
-        <v>3200</v>
+        <v>1200</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>00073994</t>
+          <t>00073995</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -36606,7 +36606,7 @@
         </is>
       </c>
       <c r="Y81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z81" t="n">
         <v>1</v>
@@ -36618,12 +36618,12 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t xml:space="preserve">K </t>
+          <t xml:space="preserve">S </t>
         </is>
       </c>
       <c r="AF81" s="1" t="n">
@@ -36648,7 +36648,7 @@
         </is>
       </c>
       <c r="AM81" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="AN81" t="n">
         <v>0</v>
@@ -36660,7 +36660,7 @@
         <v>0</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="AR81" t="n">
         <v>0</v>
@@ -36783,10 +36783,10 @@
         <v>0</v>
       </c>
       <c r="CF81" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="CG81" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="CH81" t="n">
         <v>0</v>
@@ -36965,62 +36965,62 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0012</t>
+          <t>0019</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Y6-5</t>
+          <t>W6-3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>00079873</t>
+          <t>00080065</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>50080-AY0B- 680X200F-ABG1F</t>
+          <t>15020-AX5R-1440X300F-A   P</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-ABG1C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="Q82" t="n">
-        <v>1200</v>
+        <v>6000</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>接続,SEC</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -37035,7 +37035,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>00073995</t>
+          <t>00074179</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>0012</t>
+          <t>0019</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -37062,11 +37062,11 @@
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
@@ -37075,20 +37075,20 @@
         </is>
       </c>
       <c r="AF82" s="1" t="n">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="AG82" s="1" t="n">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="AH82" s="1" t="n">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="AI82" t="inlineStr"/>
       <c r="AJ82" s="1" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="AK82" s="1" t="n">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         </is>
       </c>
       <c r="AM82" t="n">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="AN82" t="n">
         <v>0</v>
@@ -37108,7 +37108,7 @@
         <v>0</v>
       </c>
       <c r="AQ82" t="n">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="AR82" t="n">
         <v>0</v>
@@ -37234,7 +37234,7 @@
         <v>0</v>
       </c>
       <c r="CG82" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="CH82" t="n">
         <v>0</v>
@@ -37249,10 +37249,10 @@
         <v>0</v>
       </c>
       <c r="CL82" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="CM82" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="CN82" t="n">
         <v>0</v>
@@ -37423,7 +37423,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H83" s="1" t="n">
@@ -37431,12 +37431,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>W6-3</t>
+          <t>W6-4</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>00080065</t>
+          <t>00080067</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -37457,7 +37457,7 @@
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>EC,検査</t>
+          <t>スリット,EC,検査</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -37483,7 +37483,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>00074179</t>
+          <t>00074180</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -37523,20 +37523,20 @@
         </is>
       </c>
       <c r="AF83" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="AG83" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="AH83" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="AK83" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
@@ -37700,19 +37700,19 @@
         <v>0</v>
       </c>
       <c r="CM83" t="n">
+        <v>1200</v>
+      </c>
+      <c r="CN83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP83" t="n">
         <v>3600</v>
       </c>
-      <c r="CN83" t="n">
-        <v>2400</v>
-      </c>
-      <c r="CO83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP83" t="n">
-        <v>0</v>
-      </c>
       <c r="CQ83" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="CR83" t="n">
         <v>0</v>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H84" s="1" t="n">
@@ -37879,12 +37879,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>W6-4</t>
+          <t>W6-5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>00080067</t>
+          <t>00080066</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -37905,18 +37905,18 @@
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="Q84" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>スリット,EC,検査</t>
+          <t>EC,検査</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -37931,7 +37931,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>00074180</t>
+          <t>00074181</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -37958,7 +37958,7 @@
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
@@ -37971,20 +37971,20 @@
         </is>
       </c>
       <c r="AF84" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="AG84" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="AH84" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="AI84" t="inlineStr"/>
       <c r="AJ84" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="AK84" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         </is>
       </c>
       <c r="AM84" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="AN84" t="n">
         <v>0</v>
@@ -38004,7 +38004,7 @@
         <v>0</v>
       </c>
       <c r="AQ84" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="AR84" t="n">
         <v>0</v>
@@ -38151,7 +38151,7 @@
         <v>0</v>
       </c>
       <c r="CN84" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="CO84" t="n">
         <v>0</v>
@@ -38160,13 +38160,13 @@
         <v>0</v>
       </c>
       <c r="CQ84" t="n">
+        <v>2400</v>
+      </c>
+      <c r="CR84" t="n">
         <v>3600</v>
       </c>
-      <c r="CR84" t="n">
-        <v>1200</v>
-      </c>
       <c r="CS84" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="CT84" t="n">
         <v>0</v>
@@ -38283,454 +38283,6 @@
         <v>0</v>
       </c>
       <c r="EF84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>520201</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>湖南工場01本倉庫</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>熱融着機　湖南</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0019</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>検査</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>003</t>
-        </is>
-      </c>
-      <c r="H85" s="1" t="n">
-        <v>46168</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>W6-5</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>00080066</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>6780</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>6783</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>15020-AX5R-1440X300F-A   P</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
-        </is>
-      </c>
-      <c r="P85" t="n">
-        <v>9000</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>9000</v>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>EC,検査</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>東レ株式会社</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>自動車材料事業部</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>00074181</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>0019</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Y85" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
-      <c r="AC85" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>EC機　湖南</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S </t>
-        </is>
-      </c>
-      <c r="AF85" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="AG85" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="AH85" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="AI85" t="inlineStr"/>
-      <c r="AJ85" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="AK85" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>0:未完</t>
-        </is>
-      </c>
-      <c r="AM85" t="n">
-        <v>9000</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ85" t="n">
-        <v>9000</v>
-      </c>
-      <c r="AR85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR85" t="n">
-        <v>2400</v>
-      </c>
-      <c r="CS85" t="n">
-        <v>3600</v>
-      </c>
-      <c r="CT85" t="n">
-        <v>3000</v>
-      </c>
-      <c r="CU85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED85" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF85" t="n">
         <v>0</v>
       </c>
     </row>
